--- a/data/raw/prices_wb.xlsx
+++ b/data/raw/prices_wb.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I158"/>
+  <dimension ref="A1:I160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,26 +466,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин моногидрат Creatine Monohydrate, без вкуса 200 гр</t>
+          <t>МИРРОЛЛА Омега 3-6-9 100 капсул</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>640</v>
+        <v>329</v>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WB арт.4219394</t>
+          <t>WB арт.285430974</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -494,37 +494,37 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>480</v>
+        <v>197</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин Creatine Monohydrate 100% Pure (без вкуса), 500 гр</t>
+          <t>miamai Рыбий жир, Омега 3 капсулы массой 1200 мг 200 капс</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>1411</v>
+        <v>1809</v>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WB арт.13257465</t>
+          <t>WB арт.1046789814</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -533,37 +533,37 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>423</v>
+        <v>543</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин Creatine Monohydrate, Вишня 200 гр</t>
+          <t>ARCTICHEALTH Омега-3 900 мг и D3 2000 МЕ, 30 капсул (1400 мг)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>660</v>
+        <v>1635</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>WB арт.120930475</t>
+          <t>WB арт.533196308</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -572,37 +572,37 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>495</v>
+        <v>3270</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин Creatine Monohydrate, Энергетик 200 гр</t>
+          <t>mirrolla Омега 3 60 капсул</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>660</v>
+        <v>1386</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>WB арт.228766204</t>
+          <t>WB арт.236265488</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>495</v>
+        <v>1386</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -622,26 +622,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин Creatine Monohydrate, Ананас 200 гр</t>
+          <t>РеалКапс Омега-3 капс 1,4 N90</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>845</v>
+        <v>1596</v>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WB арт.120930473</t>
+          <t>WB арт.1289833341</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>634</v>
+        <v>31920</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -661,26 +661,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин Creatine Monohydrate, Цитрусовый микс 200 гр</t>
+          <t>SWISS Омега 3 Нордик Ультимат Турция 200 капсул</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>1674</v>
       </c>
       <c r="E7" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>WB арт.120930474</t>
+          <t>WB арт.869146483</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -689,37 +689,37 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>422</v>
+        <v>502</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин Creatine Monohydrate, Вишня 500 гр</t>
+          <t>NOW Omega-3 Fish Oil 100 капсул, Рыбий жир в капсулах</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>1525</v>
+        <v>1000</v>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>WB арт.183766036</t>
+          <t>WB арт.577270229</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>458</v>
+        <v>600</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -739,26 +739,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин Creatine Monohydrate Pineapple (ананас), 500 гр</t>
+          <t>RealCaps Омега-3 90 капсул</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>1490</v>
+        <v>631</v>
       </c>
       <c r="E9" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>WB арт.183766034</t>
+          <t>WB арт.938951741</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -778,26 +778,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Омега-3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BIOVIN Креатин моногидрат порошок, спортивное питание creatine 300г</t>
+          <t>ФармГрупп Омега 3 рыбий жир 300 капсул</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="E10" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WB арт.59102656</t>
+          <t>WB арт.978166657</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -817,26 +817,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Креатин</t>
+          <t>Витамин D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prime Kraft Креатин моногидрат микронизированный, фруктовый пунш 200 гр</t>
+          <t>NOW Витамин Д3 2000 (vitamin D3), 120 капсул</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>668</v>
+        <v>821</v>
       </c>
       <c r="E11" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WB арт.213577274</t>
+          <t>WB арт.1248367953</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -845,37 +845,37 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>501</v>
+        <v>205</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>Витамин D</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>МИРРОЛЛА Омега 3-6-9 100 капсул</t>
+          <t>VPLab Витамин Д3 2000 МЕ для сердца, костей и зубов 180капсул</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D12" t="n">
-        <v>329</v>
+        <v>709</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WB арт.285430974</t>
+          <t>WB арт.295624491</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -895,26 +895,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>Витамин D</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>miamai Рыбий жир, Омега 3 капсулы массой 1200 мг 200 капс</t>
+          <t>mirrolla Витамин Д3 2000 МЕ для взрослых и детей, 30 капсул</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>1809</v>
+        <v>373</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WB арт.1046789814</t>
+          <t>WB арт.65929966</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -923,37 +923,37 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>543</v>
+        <v>373</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>Витамин D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARCTICHEALTH Омега-3 900 мг и D3 2000 МЕ, 30 капсул (1400 мг)</t>
+          <t>NOW Высокоэффективный витамин Д-3 2000 МЕ 303 мг 120 капс</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D14" t="n">
-        <v>1635</v>
+        <v>1323</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WB арт.533196308</t>
+          <t>WB арт.1292014351</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3270</v>
+        <v>331</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>Витамин D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mirrolla Омега 3 60 капсул</t>
+          <t>Dr. Nansen Витамин D3 2000 МЕ Доктор Нансен 365 капсул</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>365</v>
       </c>
       <c r="D15" t="n">
-        <v>1386</v>
+        <v>1340</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WB арт.236265488</t>
+          <t>WB арт.589102224</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1386</v>
+        <v>110</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>РеалКапс Омега-3 капс 1,4 N90</t>
+          <t>GLS pharmaceuticals Витамин В12 GLS капсулы по 400 мг 60 шт</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>1596</v>
+        <v>468</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WB арт.1289833341</t>
+          <t>WB арт.822682279</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1040,37 +1040,37 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>31920</v>
+        <v>234</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SWISS Омега 3 Нордик Ультимат Турция 200 капсул</t>
+          <t>swanson Витамин В12 Цианокобаламин 500 мкг Cyanocobalamin 250 капсул</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D17" t="n">
-        <v>1674</v>
+        <v>1139</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WB арт.869146483</t>
+          <t>WB арт.232293435</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1079,37 +1079,37 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>502</v>
+        <v>137</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NOW Omega-3 Fish Oil 100 капсул, Рыбий жир в капсулах</t>
+          <t>GOODDAY Витамин B12 60 таблеток</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>1000</v>
+        <v>1087</v>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WB арт.577270229</t>
+          <t>WB арт.706034758</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1118,37 +1118,37 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>600</v>
+        <v>544</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RealCaps Омега-3 90 капсул</t>
+          <t>ВИТАМИР Метилкобаламин Витамин В12 (B12) 60 таб</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
-        <v>631</v>
+        <v>580</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WB арт.938951741</t>
+          <t>WB арт.113050183</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1157,37 +1157,37 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>421</v>
+        <v>290</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ФармГрупп Омега 3 рыбий жир 300 капсул</t>
+          <t>NATROL Витамин B12, быстрорастворимый, 5000 мкг, 100 таблеток</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D20" t="n">
-        <v>445</v>
+        <v>1843</v>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WB арт.978166657</t>
+          <t>WB арт.447267678</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1196,37 +1196,37 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>89</v>
+        <v>553</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Витамин D</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NOW Витамин Д3 2000 (vitamin D3), 120 капсул</t>
+          <t>Vitamir Витамир Витамин В12 таблетки массой 100 мг 60 шт</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D21" t="n">
-        <v>821</v>
+        <v>226</v>
       </c>
       <c r="E21" t="n">
         <v>30</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WB арт.1248367953</t>
+          <t>WB арт.822678169</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1235,37 +1235,37 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>205</v>
+        <v>113</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Витамин D</t>
+          <t>Магний</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VPLab Витамин Д3 2000 МЕ для сердца, костей и зубов 180капсул</t>
+          <t>Green SIDE Green Side Магний 500 мг+В6 таблетки по 1500 мг 30 шт</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>709</v>
+        <v>536</v>
       </c>
       <c r="E22" t="n">
         <v>30</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WB арт.295624491</t>
+          <t>WB арт.822672205</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1274,37 +1274,37 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>118</v>
+        <v>536</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Витамин D</t>
+          <t>Магний</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mirrolla Витамин Д3 2000 МЕ для взрослых и детей, 30 капсул</t>
+          <t>Эвалар Магний В6 от стресса, 60 таблеток</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D23" t="n">
-        <v>373</v>
+        <v>536</v>
       </c>
       <c r="E23" t="n">
         <v>30</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WB арт.65929966</t>
+          <t>WB арт.891116585</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1313,37 +1313,37 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>373</v>
+        <v>268</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Витамин D</t>
+          <t>Магний</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NOW Высокоэффективный витамин Д-3 2000 МЕ 303 мг 120 капс</t>
+          <t>mirrolla Mirrolla Магний B6+В9 шипучие 20 таблеток</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>1323</v>
+        <v>220</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WB арт.1292014351</t>
+          <t>WB арт.990687543</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1352,37 +1352,37 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Витамин D</t>
+          <t>Магний</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dr. Nansen Витамин D3 2000 МЕ Доктор Нансен 365 капсул</t>
+          <t>MAXLER Maxler Магний B6 Magnesium B6 таблетки по 0,65 г 120 шт</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>365</v>
+        <v>120</v>
       </c>
       <c r="D25" t="n">
-        <v>1340</v>
+        <v>1089</v>
       </c>
       <c r="E25" t="n">
         <v>30</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WB арт.589102224</t>
+          <t>WB арт.822669873</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>110</v>
+        <v>272</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Магний</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GLS pharmaceuticals Витамин В12 GLS капсулы по 400 мг 60 шт</t>
+          <t>Магнелис Магнелис В6 таблетки покрыт.об. 48 мг+5 мг 50 шт</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D26" t="n">
-        <v>468</v>
+        <v>583</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WB арт.822682279</t>
+          <t>WB арт.822685434</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1430,37 +1430,37 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>234</v>
+        <v>350</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Кофеин</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>swanson Витамин В12 Цианокобаламин 500 мкг Cyanocobalamin 250 капсул</t>
+          <t>2SN Кофеин для энергии Caffeine 150мг 100 капсул</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="D27" t="n">
-        <v>1139</v>
+        <v>672</v>
       </c>
       <c r="E27" t="n">
         <v>30</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WB арт.232293435</t>
+          <t>WB арт.706524507</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1480,26 +1480,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Кофеин</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GOODDAY Витамин B12 60 таблеток</t>
+          <t>SportLine Nutrition Порошок Кофеин с гуараной капсулы 125 шт</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D28" t="n">
-        <v>1087</v>
+        <v>1108</v>
       </c>
       <c r="E28" t="n">
         <v>30</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WB арт.706034758</t>
+          <t>WB арт.11957782</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1508,37 +1508,37 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>544</v>
+        <v>266</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Кофеин</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ВИТАМИР Метилкобаламин Витамин В12 (B12) 60 таб</t>
+          <t>Be First BF Кофеин термогеник Caffeine стимулятор ЦНС, 90 капсул</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D29" t="n">
-        <v>580</v>
+        <v>1084</v>
       </c>
       <c r="E29" t="n">
         <v>30</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WB арт.113050183</t>
+          <t>WB арт.156393514</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1558,26 +1558,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Кофеин</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NATROL Витамин B12, быстрорастворимый, 5000 мкг, 100 таблеток</t>
+          <t>Mutant Кофеин в таблетках 200 мг Core Series 240 шт</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="D30" t="n">
-        <v>1843</v>
+        <v>1784</v>
       </c>
       <c r="E30" t="n">
         <v>30</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WB арт.447267678</t>
+          <t>WB арт.723101918</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1586,37 +1586,37 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>553</v>
+        <v>223</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Кофеин</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vitamir Витамир Витамин В12 таблетки массой 100 мг 60 шт</t>
+          <t>Эвалар Кофеин натуральный 200 мг, для энергии, 60 капсул</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>60</v>
       </c>
       <c r="D31" t="n">
-        <v>226</v>
+        <v>1409</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WB арт.822678169</t>
+          <t>WB арт.507823815</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1625,37 +1625,37 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>113</v>
+        <v>704</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Магний</t>
+          <t>Кофеин</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Green SIDE Green Side Магний 500 мг+В6 таблетки по 1500 мг 30 шт</t>
+          <t>Olimp Sport Nutrition Кофеин в капсулах спортивный Caffeine Kick 200мг, 60 шт</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>536</v>
+        <v>1060</v>
       </c>
       <c r="E32" t="n">
         <v>30</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WB арт.822672205</t>
+          <t>WB арт.226453842</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1675,26 +1675,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Магний</t>
+          <t>Кофеин</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Эвалар Магний В6 от стресса, 60 таблеток</t>
+          <t>aTech nutrition Кофеин Энергетик 90 капсул</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>536</v>
+        <v>508</v>
       </c>
       <c r="E33" t="n">
         <v>30</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WB арт.891116585</t>
+          <t>WB арт.169513212</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1714,26 +1714,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Магний</t>
+          <t>L-Теанин</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>mirrolla Mirrolla Магний B6+В9 шипучие 20 таблеток</t>
+          <t>NOW Л-Теанин 200мг L-Theanine 60 капсул</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D34" t="n">
-        <v>220</v>
+        <v>1734</v>
       </c>
       <c r="E34" t="n">
         <v>30</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WB арт.990687543</t>
+          <t>WB арт.391324872</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1742,37 +1742,37 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>330</v>
+        <v>867</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Магний</t>
+          <t>L-Теанин</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MAXLER Maxler Магний B6 Magnesium B6 таблетки по 0,65 г 120 шт</t>
+          <t>Эвалар Теанин капсулы 30 шт</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>1089</v>
+        <v>709</v>
       </c>
       <c r="E35" t="n">
         <v>30</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WB арт.822669873</t>
+          <t>WB арт.40021057</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1781,37 +1781,37 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>272</v>
+        <v>709</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Магний</t>
+          <t>L-Теанин</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Магнелис Магнелис В6 таблетки покрыт.об. 48 мг+5 мг 50 шт</t>
+          <t>HealthIs «L-теанин» («L-theanine»), 90 капсул</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>583</v>
+        <v>629</v>
       </c>
       <c r="E36" t="n">
         <v>30</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WB арт.822685434</t>
+          <t>WB арт.1242186753</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1820,37 +1820,37 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>350</v>
+        <v>210</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Кофеин</t>
+          <t>L-Теанин</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2SN Кофеин для энергии Caffeine 150мг 100 капсул</t>
+          <t>NOW L-Тианин L-Theanine 200 мг 60 капсул</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D37" t="n">
-        <v>672</v>
+        <v>970</v>
       </c>
       <c r="E37" t="n">
         <v>30</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WB арт.706524507</t>
+          <t>WB арт.323251921</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>202</v>
+        <v>485</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1870,26 +1870,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Кофеин</t>
+          <t>L-Теанин</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SportLine Nutrition Порошок Кофеин с гуараной капсулы 125 шт</t>
+          <t>NOW L Теанин для нервной системы и памяти L Theanine 120 капсул</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D38" t="n">
-        <v>1108</v>
+        <v>3270</v>
       </c>
       <c r="E38" t="n">
         <v>30</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WB арт.11957782</t>
+          <t>WB арт.244879621</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1898,37 +1898,37 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>266</v>
+        <v>818</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Кофеин</t>
+          <t>Бакопа</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Be First BF Кофеин термогеник Caffeine стимулятор ЦНС, 90 капсул</t>
+          <t>NewOrganic Бакопа Монье 30 капсул по 500 мг Bacopa Monnieri</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>1084</v>
+        <v>846</v>
       </c>
       <c r="E39" t="n">
         <v>30</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>WB арт.156393514</t>
+          <t>WB арт.142620729</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1937,37 +1937,37 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>361</v>
+        <v>846</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Кофеин</t>
+          <t>Бакопа</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mutant Кофеин в таблетках 200 мг Core Series 240 шт</t>
+          <t>Alantra Брахми капсулы Алантра, 500 мг*60 шт</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="D40" t="n">
-        <v>1784</v>
+        <v>2043</v>
       </c>
       <c r="E40" t="n">
         <v>30</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>WB арт.723101918</t>
+          <t>WB арт.978008067</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1976,37 +1976,37 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>223</v>
+        <v>1021</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Кофеин</t>
+          <t>Бакопа</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Эвалар Кофеин натуральный 200 мг, для энергии, 60 капсул</t>
+          <t>Натураведа Бакопа монье для мозга 2 уп по 60 таб</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>60</v>
       </c>
       <c r="D41" t="n">
-        <v>1409</v>
+        <v>722</v>
       </c>
       <c r="E41" t="n">
         <v>30</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>WB арт.507823815</t>
+          <t>WB арт.529349243</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2015,37 +2015,37 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>704</v>
+        <v>361</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Кофеин</t>
+          <t>Бакопа</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Olimp Sport Nutrition Кофеин в капсулах спортивный Caffeine Kick 200мг, 60 шт</t>
+          <t>Fungiline Бакопа Монье Bacopa Monnieri • 60 капсул</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>60</v>
       </c>
       <c r="D42" t="n">
-        <v>1060</v>
+        <v>1412</v>
       </c>
       <c r="E42" t="n">
         <v>30</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WB арт.226453842</t>
+          <t>WB арт.217054864</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2054,37 +2054,37 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>530</v>
+        <v>706</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Кофеин</t>
+          <t>Бакопа</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>aTech nutrition Кофеин Энергетик 90 капсул</t>
+          <t>Для здоровья Бакопа монье капсулы 60 шт</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="E43" t="n">
         <v>30</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>WB арт.169513212</t>
+          <t>WB арт.210667217</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>169</v>
+        <v>262</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2104,26 +2104,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L-Теанин</t>
+          <t>Бакопа</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NOW Л-Теанин 200мг L-Theanine 60 капсул</t>
+          <t>VirorDea Бакопа Монье и Ежовик Гребенчатый (lions Mane) 240 капсул</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="D44" t="n">
-        <v>1734</v>
+        <v>709</v>
       </c>
       <c r="E44" t="n">
         <v>30</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>WB арт.391324872</t>
+          <t>WB арт.303467373</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2132,37 +2132,37 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>867</v>
+        <v>89</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L-Теанин</t>
+          <t>Бакопа</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Эвалар Теанин капсулы 30 шт</t>
+          <t>aTech nutrition БАД Бакопа Монье 60 + 60 капсул</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>709</v>
+        <v>797</v>
       </c>
       <c r="E45" t="n">
         <v>30</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>WB арт.40021057</t>
+          <t>WB арт.178086244</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>709</v>
+        <v>398</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2182,26 +2182,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L-Теанин</t>
+          <t>Ежовик</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HealthIs «L-теанин» («L-theanine»), 90 капсул</t>
+          <t>ГрибNik Ежовик гребенчатый Lions Mane мицелий 200 капсул</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="D46" t="n">
-        <v>629</v>
+        <v>920</v>
       </c>
       <c r="E46" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>WB арт.1242186753</t>
+          <t>WB арт.876874615</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2221,26 +2221,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L-Теанин</t>
+          <t>Ежовик</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NOW L-Тианин L-Theanine 200 мг 60 капсул</t>
+          <t>ГрибNik Ежовик гребенчатый Lions Mane мицелий 120 капсул 500мг</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D47" t="n">
-        <v>970</v>
+        <v>760</v>
       </c>
       <c r="E47" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>WB арт.323251921</t>
+          <t>WB арт.142604767</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>485</v>
+        <v>380</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2260,26 +2260,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L-Теанин</t>
+          <t>Ежовик</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NOW L Теанин для нервной системы и памяти L Theanine 120 капсул</t>
+          <t>Сашера-мед Ежовик гребенчатый с лецитином для мозга 2 шт</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3270</v>
+        <v>943</v>
       </c>
       <c r="E48" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>WB арт.244879621</t>
+          <t>WB арт.655827949</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>818</v>
+        <v>28290</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2299,26 +2299,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Бакопа</t>
+          <t>Ежовик</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Аэлита Агрофирма Бакопа семена 3 шт</t>
+          <t>Эвалар Ежовик гребенчатый 300 мг Lion's mane мицелий, 120 капсул</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D49" t="n">
-        <v>539</v>
+        <v>2040</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WB арт.218265741</t>
+          <t>WB арт.862262569</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2327,37 +2327,37 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5390</v>
+        <v>1020</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Бакопа</t>
+          <t>Ежовик</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Агрофирма АЭЛИТА Семена Бакопы раскидистой Драже 3 шт</t>
+          <t>Эвалар Ежовик гребенчатый Lion’s mane 300 мг капсулы по 0,5 г 60 шт</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D50" t="n">
-        <v>288</v>
+        <v>1216</v>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>WB арт.684604174</t>
+          <t>WB арт.822685874</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2880</v>
+        <v>1216</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -2382,21 +2382,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ГрибNik Ежовик гребенчатый Lions Mane мицелий 200 капсул</t>
+          <t xml:space="preserve"> Ежовик Гребенчатый капсулы 90 шт Экстракт гриба lions mane</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="D51" t="n">
-        <v>920</v>
+        <v>500</v>
       </c>
       <c r="E51" t="n">
         <v>60</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WB арт.876874615</t>
+          <t>WB арт.636128821</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2421,21 +2421,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ГрибNik Ежовик гребенчатый Lions Mane мицелий 120 капсул 500мг</t>
+          <t>NOW Foods Ежовик Гребенчатый Lion's mane 500 мг 60 капсул</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="E52" t="n">
         <v>60</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WB арт.142604767</t>
+          <t>WB арт.1418115688</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2444,11 +2444,11 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>380</v>
+        <v>752</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -2460,21 +2460,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Сашера-мед Ежовик гребенчатый с лецитином для мозга 2 шт</t>
+          <t>Altay Superfood Ежовик гребенчатый капсулы мицелий 120 шт</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="D53" t="n">
-        <v>943</v>
+        <v>560</v>
       </c>
       <c r="E53" t="n">
         <v>60</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>WB арт.655827949</t>
+          <t>WB арт.1331819703</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28290</v>
+        <v>280</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -2499,21 +2499,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Эвалар Ежовик гребенчатый 300 мг Lion's mane мицелий, 120 капсул</t>
+          <t>vitmins Ежовик гребенчатый, 120 капсул</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>120</v>
       </c>
       <c r="D54" t="n">
-        <v>2040</v>
+        <v>846</v>
       </c>
       <c r="E54" t="n">
         <v>60</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>WB арт.862262569</t>
+          <t>WB арт.437391719</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2522,11 +2522,11 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1020</v>
+        <v>423</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -2538,21 +2538,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Эвалар Ежовик гребенчатый Lion’s mane 300 мг капсулы по 0,5 г 60 шт</t>
+          <t>Эвалар Ежовик гребенчатый 300 мг Lion's mane мицелий, 60 капсул</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="E55" t="n">
         <v>60</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>WB арт.822685874</t>
+          <t>WB арт.165911558</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ежовик Гребенчатый капсулы 90 шт Экстракт гриба lions mane</t>
+          <t>Siwani Ежовик гребенчатый 700 мг 90 капсул</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>90</v>
       </c>
       <c r="D56" t="n">
-        <v>500</v>
+        <v>809</v>
       </c>
       <c r="E56" t="n">
         <v>60</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>WB арт.636128821</t>
+          <t>WB арт.215926791</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2600,37 +2600,37 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>333</v>
+        <v>539</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ежовик</t>
+          <t>Гинкго</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NOW Foods Ежовик Гребенчатый Lion's mane 500 мг 60 капсул</t>
+          <t>NOW Гинкго Билоба Ginkgo Biloba 120 mg, 50 капсул</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>752</v>
+        <v>720</v>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>WB арт.1418115688</t>
+          <t>WB арт.616166162</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2639,37 +2639,37 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>752</v>
+        <v>432</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ежовик</t>
+          <t>Гинкго</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Altay Superfood Ежовик гребенчатый капсулы мицелий 120 шт</t>
+          <t xml:space="preserve"> Гинкго Билоба 500 мг 180 капсул для памяти и работы мозга</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D58" t="n">
-        <v>560</v>
+        <v>835</v>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>WB арт.1331819703</t>
+          <t>WB арт.1028709974</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ежовик</t>
+          <t>Гинкго</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>vitmins Ежовик гребенчатый, 120 капсул</t>
+          <t>ГрибNik Экстракт Гинкго Билоба + коэнзим q10 60 капсул</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D59" t="n">
-        <v>846</v>
+        <v>576</v>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>WB арт.437391719</t>
+          <t>WB арт.879404447</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2717,37 +2717,37 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>423</v>
+        <v>288</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ежовик</t>
+          <t>Гинкго</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Эвалар Ежовик гребенчатый 300 мг Lion's mane мицелий, 60 капсул</t>
+          <t>OVER Глицин + Гинкго Билоба + Готу Кола, 60 капсул</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>60</v>
       </c>
       <c r="D60" t="n">
-        <v>1211</v>
+        <v>674</v>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>WB арт.165911558</t>
+          <t>WB арт.167807321</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2756,37 +2756,37 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1211</v>
+        <v>337</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ежовик</t>
+          <t>Гинкго</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Siwani Ежовик гребенчатый 700 мг 90 капсул</t>
+          <t>Эвалар Гинкго Билоба 40 мг, таб. 40 шт</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D61" t="n">
-        <v>809</v>
+        <v>420</v>
       </c>
       <c r="E61" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>WB арт.215926791</t>
+          <t>WB арт.51853968</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>539</v>
+        <v>315</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NOW Гинкго Билоба Ginkgo Biloba 120 mg, 50 капсул</t>
+          <t>Гинкго Билоба Гинкго Билоба таблетки покрыт.плен.об. 40 мг 30 шт</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D62" t="n">
-        <v>720</v>
+        <v>395</v>
       </c>
       <c r="E62" t="n">
         <v>30</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>WB арт.616166162</t>
+          <t>WB арт.822666921</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2845,26 +2845,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Гинкго</t>
+          <t>Родиола</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Гинкго Билоба 500 мг 180 капсул для памяти и работы мозга</t>
+          <t>GLS pharmaceuticals Родиола розовая экстракт GLS капсулы по 400 мг 60 шт</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="D63" t="n">
-        <v>835</v>
+        <v>645</v>
       </c>
       <c r="E63" t="n">
         <v>30</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>WB арт.1028709974</t>
+          <t>WB арт.822665930</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2873,37 +2873,37 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>139</v>
+        <v>322</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Гинкго</t>
+          <t>Родиола</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ГрибNik Экстракт Гинкго Билоба + коэнзим q10 60 капсул</t>
+          <t>Экстракт ВИС Родиолы розовой экстракт-ВИС капсулы массой 0,4 г 30 шт</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D64" t="n">
-        <v>576</v>
+        <v>299</v>
       </c>
       <c r="E64" t="n">
         <v>30</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>WB арт.879404447</t>
+          <t>WB арт.822680108</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2923,26 +2923,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Гинкго</t>
+          <t>Родиола</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OVER Глицин + Гинкго Билоба + Готу Кола, 60 капсул</t>
+          <t>– Родиолы экстракт жидкий для приема внутрь 30 мл 1 шт</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>674</v>
+        <v>140</v>
       </c>
       <c r="E65" t="n">
         <v>30</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>WB арт.167807321</t>
+          <t>WB арт.822684736</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2951,37 +2951,37 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>337</v>
+        <v>4200</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Гинкго</t>
+          <t>Родиола</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Эвалар Гинкго Билоба 40 мг, таб. 40 шт</t>
+          <t>эколаб Родиола + витамин С 90 капсул</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>420</v>
+        <v>604</v>
       </c>
       <c r="E66" t="n">
         <v>30</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>WB арт.51853968</t>
+          <t>WB арт.455420502</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2990,37 +2990,37 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>315</v>
+        <v>201</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Гинкго</t>
+          <t>Фосфатидилсерин</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Гинкго Билоба Гинкго Билоба таблетки покрыт.плен.об. 40 мг 30 шт</t>
+          <t>NOW Phosphatidyl Serine Фосфатидил Серин 100 мг - 60 капсул</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D67" t="n">
-        <v>395</v>
+        <v>1839</v>
       </c>
       <c r="E67" t="n">
         <v>30</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>WB арт.822666921</t>
+          <t>WB арт.323251901</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3029,37 +3029,37 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>395</v>
+        <v>920</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Родиола</t>
+          <t>Фосфатидилсерин</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GLS pharmaceuticals Родиола розовая экстракт GLS капсулы по 400 мг 60 шт</t>
+          <t>NOW Phosphatidyl Serine 100 mg Фосфатидил Серин 100 мг 60 капсул</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>60</v>
       </c>
       <c r="D68" t="n">
-        <v>645</v>
+        <v>2586</v>
       </c>
       <c r="E68" t="n">
         <v>30</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>WB арт.822665930</t>
+          <t>WB арт.174824344</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>322</v>
+        <v>1293</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3079,26 +3079,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Родиола</t>
+          <t>Фосфатидилсерин</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Экстракт ВИС Родиолы розовой экстракт-ВИС капсулы массой 0,4 г 30 шт</t>
+          <t>GraFLab Фосфатидилсерин 510 мг, 2 банки по 60 капсул</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D69" t="n">
-        <v>299</v>
+        <v>2799</v>
       </c>
       <c r="E69" t="n">
         <v>30</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>WB арт.822680108</t>
+          <t>WB арт.560802015</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3107,37 +3107,37 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>299</v>
+        <v>1400</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Родиола</t>
+          <t>Фосфатидилсерин</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>– Родиолы экстракт жидкий для приема внутрь 30 мл 1 шт</t>
+          <t>Эвалар Когнивия Фосфатидилсерин, ноотроп,30 капсул</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>140</v>
+        <v>1994</v>
       </c>
       <c r="E70" t="n">
         <v>30</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>WB арт.822684736</t>
+          <t>WB арт.1225854064</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>4200</v>
+        <v>1994</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3157,26 +3157,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Родиола</t>
+          <t>Фосфатидилсерин</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>эколаб Родиола + витамин С 90 капсул</t>
+          <t>DHC Фосфатидилсерин для памяти и работы мозга, 60шт на 30 дней</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D71" t="n">
-        <v>604</v>
+        <v>4198</v>
       </c>
       <c r="E71" t="n">
         <v>30</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>WB арт.455420502</t>
+          <t>WB арт.432680707</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3185,11 +3185,11 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>201</v>
+        <v>2099</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -3201,21 +3201,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NOW Phosphatidyl Serine Фосфатидил Серин 100 мг - 60 капсул</t>
+          <t>Nutricost Фосфатидилсерин (Phosphatidylserine) 200 мг, 120 капсул</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D72" t="n">
-        <v>1839</v>
+        <v>4654</v>
       </c>
       <c r="E72" t="n">
         <v>30</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>WB арт.323251901</t>
+          <t>WB арт.1217737987</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>920</v>
+        <v>1164</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3240,21 +3240,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NOW Phosphatidyl Serine 100 mg Фосфатидил Серин 100 мг 60 капсул</t>
+          <t>NOW Фосфатидилсерин для памяти и мозга Phosphatidyl 60 капсул</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>60</v>
       </c>
       <c r="D73" t="n">
-        <v>2586</v>
+        <v>4365</v>
       </c>
       <c r="E73" t="n">
         <v>30</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>WB арт.174824344</t>
+          <t>WB арт.447891954</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3263,11 +3263,11 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1293</v>
+        <v>2182</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -3279,11 +3279,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GraFLab Фосфатидилсерин 510 мг, 2 банки по 60 капсул</t>
+          <t>GraFLab Фосфатидилсерин, 510 мг, 120 капсул</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D74" t="n">
         <v>2799</v>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>WB арт.560802015</t>
+          <t>WB арт.819325763</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3302,37 +3302,37 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Фосфатидилсерин</t>
+          <t>Alpha-GPC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Эвалар Когнивия Фосфатидилсерин, ноотроп,30 капсул</t>
+          <t>SNT Alpha GPC 60 капсул, СНТ Альфа Глицерофосфохолин, Альфа ГПТ</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D75" t="n">
-        <v>1994</v>
+        <v>2818</v>
       </c>
       <c r="E75" t="n">
         <v>30</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>WB арт.1225854064</t>
+          <t>WB арт.366981318</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3341,37 +3341,37 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1994</v>
+        <v>1409</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Фосфатидилсерин</t>
+          <t>Alpha-GPC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DHC Фосфатидилсерин для памяти и работы мозга, 60шт на 30 дней</t>
+          <t>SNT (Swiss Nutrition Technology) Витамин B4 (холин) SNT Alpha GPC 300 мг, 90 капсул</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D76" t="n">
-        <v>4198</v>
+        <v>3868</v>
       </c>
       <c r="E76" t="n">
         <v>30</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>WB арт.432680707</t>
+          <t>WB арт.760422846</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3380,37 +3380,37 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2099</v>
+        <v>1289</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Фосфатидилсерин</t>
+          <t>Alpha-GPC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nutricost Фосфатидилсерин (Phosphatidylserine) 200 мг, 120 капсул</t>
+          <t>Double Wood Supplements Альфа-ГФХ Alpha GPC 300 мг 60 капсул США</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D77" t="n">
-        <v>4654</v>
+        <v>3498</v>
       </c>
       <c r="E77" t="n">
         <v>30</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>WB арт.1217737987</t>
+          <t>WB арт.1360536751</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3419,37 +3419,37 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1164</v>
+        <v>1749</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Фосфатидилсерин</t>
+          <t>Alpha-GPC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NOW Фосфатидилсерин для памяти и мозга Phosphatidyl 60 капсул</t>
+          <t>EVLution Nutrition Альфа-ГФХ Alpha-GPC 600 мг 60 капсул</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>60</v>
       </c>
       <c r="D78" t="n">
-        <v>4365</v>
+        <v>1517</v>
       </c>
       <c r="E78" t="n">
         <v>30</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>WB арт.447891954</t>
+          <t>WB арт.374579604</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3458,37 +3458,37 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2182</v>
+        <v>758</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Фосфатидилсерин</t>
+          <t>Alpha-GPC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GraFLab Фосфатидилсерин, 510 мг, 120 капсул</t>
+          <t>Noxygen Alpha GPC 300мг 60 капс. ноотроп, эйфоретик, энергетик</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D79" t="n">
-        <v>2799</v>
+        <v>2970</v>
       </c>
       <c r="E79" t="n">
         <v>30</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>WB арт.819325763</t>
+          <t>WB арт.853747112</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3497,11 +3497,11 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>700</v>
+        <v>1485</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -3513,21 +3513,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SNT Alpha GPC 60 капсул, СНТ Альфа Глицерофосфохолин, Альфа ГПТ</t>
+          <t xml:space="preserve"> AlphaGPC Альфа ГПС99% Холин400mg60 капсул"Pure Brain Power"</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>60</v>
       </c>
       <c r="D80" t="n">
-        <v>2818</v>
+        <v>1584</v>
       </c>
       <c r="E80" t="n">
         <v>30</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>WB арт.366981318</t>
+          <t>WB арт.447701014</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3536,11 +3536,11 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1409</v>
+        <v>792</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -3552,21 +3552,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SNT (Swiss Nutrition Technology) Витамин B4 (холин) SNT Alpha GPC 300 мг, 90 капсул</t>
+          <t xml:space="preserve"> SNT Alpha GPC 90 капсул</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>90</v>
       </c>
       <c r="D81" t="n">
-        <v>3868</v>
+        <v>3947</v>
       </c>
       <c r="E81" t="n">
         <v>30</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>WB арт.760422846</t>
+          <t>WB арт.382161877</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3575,37 +3575,37 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1289</v>
+        <v>1316</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alpha-GPC</t>
+          <t>CDP-холин</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Double Wood Supplements Альфа-ГФХ Alpha GPC 300 мг 60 капсул США</t>
+          <t xml:space="preserve"> Рекогнан раствор для приема внутрь 100 мг мл 10 мл пак 10 шт</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>3498</v>
+        <v>1824</v>
       </c>
       <c r="E82" t="n">
         <v>30</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>WB арт.1360536751</t>
+          <t>WB арт.822670208</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1749</v>
+        <v>5472</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3625,26 +3625,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alpha-GPC</t>
+          <t>CDP-холин</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EVLution Nutrition Альфа-ГФХ Alpha-GPC 600 мг 60 капсул</t>
+          <t>Нейпилепт Нейпилепт раствор для в в и в м введ.125 мг мл 4 мл 5 шт</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>1517</v>
+        <v>271</v>
       </c>
       <c r="E83" t="n">
         <v>30</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>WB арт.374579604</t>
+          <t>WB арт.822679409</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>758</v>
+        <v>1626</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3664,26 +3664,26 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alpha-GPC</t>
+          <t>CDP-холин</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Noxygen Alpha GPC 300мг 60 капс. ноотроп, эйфоретик, энергетик</t>
+          <t>Nutricost ЦДФ холин, 300 мг, 60 капсул</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>60</v>
       </c>
       <c r="D84" t="n">
-        <v>2970</v>
+        <v>3714</v>
       </c>
       <c r="E84" t="n">
         <v>30</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>WB арт.853747112</t>
+          <t>WB арт.1124416138</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3692,37 +3692,37 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1485</v>
+        <v>1857</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alpha-GPC</t>
+          <t>Гуперзин А</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AlphaGPC Альфа ГПС99% Холин400mg60 капсул"Pure Brain Power"</t>
+          <t>Double Wood Supplements Гуперзин-А Huperzine A 200 мкг 120 таблеток США</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D85" t="n">
-        <v>1584</v>
+        <v>3667</v>
       </c>
       <c r="E85" t="n">
         <v>30</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>WB арт.447701014</t>
+          <t>WB арт.1360478172</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>792</v>
+        <v>917</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3742,26 +3742,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alpha-GPC</t>
+          <t>Гуперзин А</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SNT Alpha GPC 90 капсул</t>
+          <t>Double Wood Supplements Гуперзин-А Huperzine A 200 мкг 120 таблеток</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D86" t="n">
-        <v>3947</v>
+        <v>3949</v>
       </c>
       <c r="E86" t="n">
         <v>30</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WB арт.382161877</t>
+          <t>WB арт.429114911</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1316</v>
+        <v>987</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3781,26 +3781,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CDP-холин</t>
+          <t>Гуперзин А</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Рекогнан раствор для приема внутрь 100 мг мл 10 мл пак 10 шт</t>
+          <t>Nutricost Гуперзин-A 200 мкг, для памяти, 240 капсул</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="D87" t="n">
-        <v>1824</v>
+        <v>11280</v>
       </c>
       <c r="E87" t="n">
         <v>30</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WB арт.822670208</t>
+          <t>WB арт.1468248047</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5472</v>
+        <v>1410</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3820,26 +3820,26 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CDP-холин</t>
+          <t>Гуперзин А</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Нейпилепт Нейпилепт раствор для в в и в м введ.125 мг мл 4 мл 5 шт</t>
+          <t xml:space="preserve"> Гуперзин А, 200 мкг, 120 капсул</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="D88" t="n">
-        <v>271</v>
+        <v>4229</v>
       </c>
       <c r="E88" t="n">
         <v>30</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>WB арт.822679409</t>
+          <t>WB арт.1392396224</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3848,37 +3848,37 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1626</v>
+        <v>1057</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CDP-холин</t>
+          <t>Гуперзин А</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nutricost ЦДФ холин, 300 мг, 60 капсул</t>
+          <t>Nutricost Гуперзин-A, 200 мкг, 240 капсул</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="D89" t="n">
-        <v>3714</v>
+        <v>4088</v>
       </c>
       <c r="E89" t="n">
         <v>30</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>WB арт.1124416138</t>
+          <t>WB арт.419117169</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3887,11 +3887,11 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1857</v>
+        <v>511</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -3903,21 +3903,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Double Wood Supplements Гуперзин-А Huperzine A 200 мкг 120 таблеток США</t>
+          <t xml:space="preserve"> Гуперзин А, 200 мкг, 120 капсул</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>120</v>
       </c>
       <c r="D90" t="n">
-        <v>3667</v>
+        <v>3722</v>
       </c>
       <c r="E90" t="n">
         <v>30</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>WB арт.1360478172</t>
+          <t>WB арт.1518961748</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3926,11 +3926,11 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>917</v>
+        <v>930</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -3942,21 +3942,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Double Wood Supplements Гуперзин-А Huperzine A 200 мкг 120 таблеток</t>
+          <t>Nutricost Гуперзин-A, 200 мкг, 240 капсул</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="D91" t="n">
-        <v>3949</v>
+        <v>4051</v>
       </c>
       <c r="E91" t="n">
         <v>30</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>WB арт.429114911</t>
+          <t>WB арт.1466364233</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3965,11 +3965,11 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>987</v>
+        <v>506</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -3981,21 +3981,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nutricost Гуперзин-A 200 мкг, для памяти, 240 капсул</t>
+          <t>Героменталь Героменталь капсулы по 0,4 г 60 шт</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="D92" t="n">
-        <v>11280</v>
+        <v>2295</v>
       </c>
       <c r="E92" t="n">
         <v>30</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>WB арт.1468248047</t>
+          <t>WB арт.863207657</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1410</v>
+        <v>1148</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4015,26 +4015,26 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Гуперзин А</t>
+          <t>Куркумин</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Гуперзин А, 200 мкг, 120 капсул</t>
+          <t>Provital куркумин актив 60 капсул</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D93" t="n">
-        <v>4229</v>
+        <v>1683</v>
       </c>
       <c r="E93" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>WB арт.1392396224</t>
+          <t>WB арт.972316095</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1057</v>
+        <v>1683</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4054,26 +4054,26 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Гуперзин А</t>
+          <t>Куркумин</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nutricost Гуперзин-A, 200 мкг, 240 капсул</t>
+          <t>OVER Куркумин с пиперином, 60 капсул</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="D94" t="n">
-        <v>4088</v>
+        <v>467</v>
       </c>
       <c r="E94" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>WB арт.419117169</t>
+          <t>WB арт.167929799</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>511</v>
+        <v>467</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4093,26 +4093,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Гуперзин А</t>
+          <t>Куркумин</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Гуперзин А, 200 мкг, 120 капсул</t>
+          <t>Sri Sri Турмерик Плюс - Куркума с черным перцем, 60 таб</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D95" t="n">
-        <v>3722</v>
+        <v>342</v>
       </c>
       <c r="E95" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>WB арт.1518961748</t>
+          <t>WB арт.526086965</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4121,37 +4121,37 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>930</v>
+        <v>342</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Гуперзин А</t>
+          <t>Куркумин</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nutricost Гуперзин-A, 200 мкг, 240 капсул</t>
+          <t>NOW NUTRITION Куркума Экстракт 665 мг Curcumin Turmeric 60 капсул</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="D96" t="n">
-        <v>4051</v>
+        <v>750</v>
       </c>
       <c r="E96" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>WB арт.1466364233</t>
+          <t>WB арт.824823121</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4160,37 +4160,37 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>506</v>
+        <v>750</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Гуперзин А</t>
+          <t>Куркумин</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Героменталь Героменталь капсулы по 0,4 г 60 шт</t>
+          <t>California Gold Nutrition Куркумин для суставов и иммунитета, 120 капсул</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D97" t="n">
-        <v>2295</v>
+        <v>679</v>
       </c>
       <c r="E97" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>WB арт.863207657</t>
+          <t>WB арт.1252722236</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4199,11 +4199,11 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1148</v>
+        <v>340</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -4215,21 +4215,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Provital куркумин актив 60 капсул</t>
+          <t>Куркумин Куркумин 50 мг липосомальный капсулы массой 548 мг 30 шт</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D98" t="n">
-        <v>1683</v>
+        <v>2553</v>
       </c>
       <c r="E98" t="n">
         <v>60</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>WB арт.972316095</t>
+          <t>WB арт.863196146</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1683</v>
+        <v>5106</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OVER Куркумин с пиперином, 60 капсул</t>
+          <t>NOW FOODS / NOW Куркумин 665 мг 60 капсул NOW</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>60</v>
       </c>
       <c r="D99" t="n">
-        <v>467</v>
+        <v>820</v>
       </c>
       <c r="E99" t="n">
         <v>60</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>WB арт.167929799</t>
+          <t>WB арт.1258779494</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4277,11 +4277,11 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>467</v>
+        <v>820</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -4293,21 +4293,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sri Sri Турмерик Плюс - Куркума с черным перцем, 60 таб</t>
+          <t>Vitamir Куркумин Премиум таблетки покрыт.об. массой 464 мг 30 шт</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D100" t="n">
-        <v>342</v>
+        <v>681</v>
       </c>
       <c r="E100" t="n">
         <v>60</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>WB арт.526086965</t>
+          <t>WB арт.822660017</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4316,11 +4316,11 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>342</v>
+        <v>1362</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -4332,21 +4332,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NOW NUTRITION Куркума Экстракт 665 мг Curcumin Turmeric 60 капсул</t>
+          <t>Экстракт ВИС Куркумин с пиперином экстракт-ВИС капсулы массой 0,4 г 30 шт</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D101" t="n">
-        <v>750</v>
+        <v>606</v>
       </c>
       <c r="E101" t="n">
         <v>60</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>WB арт.824823121</t>
+          <t>WB арт.822682411</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>750</v>
+        <v>1212</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -4366,26 +4366,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Куркумин</t>
+          <t>Ресвератрол</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>California Gold Nutrition Куркумин для суставов и иммунитета, 120 капсул</t>
+          <t>GLS pharmaceuticals Ресвератрол 50 мг GLS капсулы по 400 мг 60 шт</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D102" t="n">
-        <v>679</v>
+        <v>812</v>
       </c>
       <c r="E102" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>WB арт.1252722236</t>
+          <t>WB арт.822674964</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>340</v>
+        <v>406</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -4405,26 +4405,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Куркумин</t>
+          <t>Ресвератрол</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Куркумин Куркумин 50 мг липосомальный капсулы массой 548 мг 30 шт</t>
+          <t>Florea Ресвератрол антиоксидант 60 капсул 200 мг</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D103" t="n">
-        <v>2553</v>
+        <v>245</v>
       </c>
       <c r="E103" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>WB арт.863196146</t>
+          <t>WB арт.504185662</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4433,37 +4433,37 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5106</v>
+        <v>122</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Куркумин</t>
+          <t>Ресвератрол</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NOW FOODS / NOW Куркумин 665 мг 60 капсул NOW</t>
+          <t>MISTERLAB Ресвератрол 250 мг, 90 капсул</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D104" t="n">
-        <v>820</v>
+        <v>1062</v>
       </c>
       <c r="E104" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>WB арт.1258779494</t>
+          <t>WB арт.1290446902</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4472,37 +4472,37 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>820</v>
+        <v>354</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Куркумин</t>
+          <t>Ресвератрол</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Vitamir Куркумин Премиум таблетки покрыт.об. массой 464 мг 30 шт</t>
+          <t>SOLGAR Ресвератрол 100 мг 60 капсул</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D105" t="n">
-        <v>681</v>
+        <v>1584</v>
       </c>
       <c r="E105" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>WB арт.822660017</t>
+          <t>WB арт.1345201919</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4511,37 +4511,37 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1362</v>
+        <v>792</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Куркумин</t>
+          <t>Ресвератрол</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Экстракт ВИС Куркумин с пиперином экстракт-ВИС капсулы массой 0,4 г 30 шт</t>
+          <t>Алтай Ресвератрол природный антиоксидант 2 шт по 60 капсул</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>606</v>
+        <v>2096</v>
       </c>
       <c r="E106" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>WB арт.822682411</t>
+          <t>WB арт.502049224</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4550,11 +4550,11 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1212</v>
+        <v>31440</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -4566,21 +4566,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GLS pharmaceuticals Ресвератрол 50 мг GLS капсулы по 400 мг 60 шт</t>
+          <t>NOW Ресвератрол RESVERATROL 200 мг 60 капсул</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>60</v>
       </c>
       <c r="D107" t="n">
-        <v>812</v>
+        <v>1585</v>
       </c>
       <c r="E107" t="n">
         <v>30</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>WB арт.822674964</t>
+          <t>WB арт.330434553</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4589,11 +4589,11 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>406</v>
+        <v>792</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -4605,21 +4605,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Florea Ресвератрол антиоксидант 60 капсул 200 мг</t>
+          <t>TETRALAB Tetralab Ресвератрол 150 мг капсулы по 340 мг 60 шт</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>60</v>
       </c>
       <c r="D108" t="n">
-        <v>245</v>
+        <v>1722</v>
       </c>
       <c r="E108" t="n">
         <v>30</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>WB арт.504185662</t>
+          <t>WB арт.822662344</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4628,37 +4628,37 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>122</v>
+        <v>861</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ресвератрол</t>
+          <t>NAC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MISTERLAB Ресвератрол 250 мг, 90 капсул</t>
+          <t>2SN НАК ацетил цистеин NAC 600mg 60 caps</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D109" t="n">
-        <v>1062</v>
+        <v>973</v>
       </c>
       <c r="E109" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>WB арт.1290446902</t>
+          <t>WB арт.580191991</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>354</v>
+        <v>973</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -4678,26 +4678,26 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ресвератрол</t>
+          <t>NAC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SOLGAR Ресвератрол 100 мг 60 капсул</t>
+          <t>MISTERLAB NAC ацетилцистеин 600 мг, 90 капсул</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D110" t="n">
-        <v>1584</v>
+        <v>1278</v>
       </c>
       <c r="E110" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>WB арт.1345201919</t>
+          <t>WB арт.848549055</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4706,37 +4706,37 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>792</v>
+        <v>852</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ресвератрол</t>
+          <t>NAC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Алтай Ресвератрол природный антиоксидант 2 шт по 60 капсул</t>
+          <t>Natures Plus NAC ацетилцистеин 1200мг для иммунитета, печени и почек 60шт</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D111" t="n">
-        <v>2096</v>
+        <v>1428</v>
       </c>
       <c r="E111" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>WB арт.502049224</t>
+          <t>WB арт.259259740</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4745,37 +4745,37 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>31440</v>
+        <v>1428</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ресвератрол</t>
+          <t>NAC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NOW Ресвератрол RESVERATROL 200 мг 60 капсул</t>
+          <t>Doctor's BEST NAC ацетилцистеин 60 капсул для иммунитета печени и почек</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>60</v>
       </c>
       <c r="D112" t="n">
-        <v>1585</v>
+        <v>1527</v>
       </c>
       <c r="E112" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>WB арт.330434553</t>
+          <t>WB арт.267523761</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4784,37 +4784,37 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>792</v>
+        <v>1527</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ресвератрол</t>
+          <t>NAC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TETRALAB Tetralab Ресвератрол 150 мг капсулы по 340 мг 60 шт</t>
+          <t>NOW NAC N-Ацетил Цистеин 600 мг 100 капсул Foods, США</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D113" t="n">
-        <v>1722</v>
+        <v>1817</v>
       </c>
       <c r="E113" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>WB арт.822662344</t>
+          <t>WB арт.1152975431</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4823,11 +4823,11 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>861</v>
+        <v>1090</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -4839,21 +4839,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2SN НАК ацетил цистеин NAC 600mg 60 caps</t>
+          <t>MISTERLAB NAC ацетилцистеин 600 мг, 90 капсул</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D114" t="n">
-        <v>973</v>
+        <v>1222</v>
       </c>
       <c r="E114" t="n">
         <v>60</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>WB арт.580191991</t>
+          <t>WB арт.1144233797</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>973</v>
+        <v>815</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MISTERLAB NAC ацетилцистеин 600 мг, 90 капсул</t>
+          <t>Life extension N-ацетил-L-цистеин NAC, 600 мг, 60 капсул</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D115" t="n">
-        <v>1278</v>
+        <v>1587</v>
       </c>
       <c r="E115" t="n">
         <v>60</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>WB арт.848549055</t>
+          <t>WB арт.1027324850</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4901,11 +4901,11 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>852</v>
+        <v>1587</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Natures Plus NAC ацетилцистеин 1200мг для иммунитета, печени и почек 60шт</t>
+          <t xml:space="preserve"> NAC 1000 мг 120 таблеток</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D116" t="n">
-        <v>1428</v>
+        <v>3667</v>
       </c>
       <c r="E116" t="n">
         <v>60</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>WB арт.259259740</t>
+          <t>WB арт.1002549742</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4940,37 +4940,37 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1428</v>
+        <v>1834</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NAC</t>
+          <t>Цинк</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Doctor's BEST NAC ацетилцистеин 60 капсул для иммунитета печени и почек</t>
+          <t>NOW NOW Цинка пиколинат 60 капсул</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>60</v>
       </c>
       <c r="D117" t="n">
-        <v>1527</v>
+        <v>1283</v>
       </c>
       <c r="E117" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>WB арт.267523761</t>
+          <t>WB арт.833816882</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1527</v>
+        <v>642</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -4990,26 +4990,26 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NAC</t>
+          <t>Цинк</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NOW NAC N-Ацетил Цистеин 600 мг 100 капсул Foods, США</t>
+          <t>Tetralab Tetralab Цинк пиколинат таблетки массой 180 мг 90 шт</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D118" t="n">
-        <v>1817</v>
+        <v>848</v>
       </c>
       <c r="E118" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>WB арт.1152975431</t>
+          <t>WB арт.822666657</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5018,37 +5018,37 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1090</v>
+        <v>283</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NAC</t>
+          <t>Цинк</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MISTERLAB NAC ацетилцистеин 600 мг, 90 капсул</t>
+          <t>Грин Сайд Green Side Цинка пиколинат №30 табл массой 300мг</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D119" t="n">
-        <v>1222</v>
+        <v>888</v>
       </c>
       <c r="E119" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>WB арт.1144233797</t>
+          <t>WB арт.1288950646</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5057,37 +5057,37 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>815</v>
+        <v>888</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NAC</t>
+          <t>Цинк</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Life extension N-ацетил-L-цистеин NAC, 600 мг, 60 капсул</t>
+          <t>From Natural Цинк пиколинат, 25 мг, 120 капсул</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D120" t="n">
-        <v>1587</v>
+        <v>409</v>
       </c>
       <c r="E120" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>WB арт.1027324850</t>
+          <t>WB арт.1088757363</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5096,37 +5096,37 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1587</v>
+        <v>102</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NAC</t>
+          <t>Цинк</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NAC 1000 мг 120 таблеток</t>
+          <t>NOW Цинк пиколинат 50 мг для иммунитета и кожи 60 капсул</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D121" t="n">
-        <v>3667</v>
+        <v>1064</v>
       </c>
       <c r="E121" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>WB арт.1002549742</t>
+          <t>WB арт.926943189</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5135,37 +5135,37 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1834</v>
+        <v>532</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Цинк</t>
+          <t>Тирозин</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NOW NOW Цинка пиколинат 60 капсул</t>
+          <t>Doctor's BEST Тирозин L-Tyrosine 500 мг для похудения, от стресса 120 caps</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D122" t="n">
-        <v>1283</v>
+        <v>1809</v>
       </c>
       <c r="E122" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>WB арт.833816882</t>
+          <t>WB арт.486140104</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5174,37 +5174,37 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>642</v>
+        <v>904</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Цинк</t>
+          <t>Тирозин</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tetralab Tetralab Цинк пиколинат таблетки массой 180 мг 90 шт</t>
+          <t>SNT L-Tyrosine 500 мг 90 капсул</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>90</v>
       </c>
       <c r="D123" t="n">
-        <v>848</v>
+        <v>2333</v>
       </c>
       <c r="E123" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>WB арт.822666657</t>
+          <t>WB арт.418345735</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5213,37 +5213,37 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>283</v>
+        <v>1555</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Цинк</t>
+          <t>Тирозин</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Грин Сайд Green Side Цинка пиколинат №30 табл массой 300мг</t>
+          <t>BioTechUSA Тирозин L-Tyrosine 1000 mg 100 капсул</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D124" t="n">
-        <v>888</v>
+        <v>1761</v>
       </c>
       <c r="E124" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>WB арт.1288950646</t>
+          <t>WB арт.629086506</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5252,37 +5252,37 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>888</v>
+        <v>1057</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Цинк</t>
+          <t>Тирозин</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>From Natural Цинк пиколинат, 25 мг, 120 капсул</t>
+          <t>NOW L-Tyrosine 500 mg 120 капсул, L-Тирозин</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>120</v>
       </c>
       <c r="D125" t="n">
-        <v>409</v>
+        <v>1103</v>
       </c>
       <c r="E125" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>WB арт.1088757363</t>
+          <t>WB арт.577311165</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>102</v>
+        <v>552</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -5302,26 +5302,26 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Цинк</t>
+          <t>Тирозин</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NOW Цинк пиколинат 50 мг для иммунитета и кожи 60 капсул</t>
+          <t>Эвалар L тирозин 500 мг, L-tyrosine, 120 таблеток</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D126" t="n">
-        <v>1064</v>
+        <v>1457</v>
       </c>
       <c r="E126" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>WB арт.926943189</t>
+          <t>WB арт.322358421</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5330,11 +5330,11 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>532</v>
+        <v>728</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -5346,21 +5346,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Doctor's BEST Тирозин L-Tyrosine 500 мг для похудения, от стресса 120 caps</t>
+          <t>SOLGAR L-тирозин 500 мг 50шт</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D127" t="n">
-        <v>1809</v>
+        <v>2130</v>
       </c>
       <c r="E127" t="n">
         <v>60</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>WB арт.486140104</t>
+          <t>WB арт.258033150</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5369,11 +5369,11 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>904</v>
+        <v>2556</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -5385,21 +5385,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SNT L-Tyrosine 500 мг 90 капсул</t>
+          <t>SNT Тирозин L-TYROSINE 500 мг 60 капс</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D128" t="n">
-        <v>2333</v>
+        <v>1792</v>
       </c>
       <c r="E128" t="n">
         <v>60</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>WB арт.418345735</t>
+          <t>WB арт.198623200</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1555</v>
+        <v>1792</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -5424,21 +5424,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BioTechUSA Тирозин L-Tyrosine 1000 mg 100 капсул</t>
+          <t>Doctor's BEST Тирозин L-Tyrosine 500 мг для похудения, от стресса 120 caps</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D129" t="n">
-        <v>1761</v>
+        <v>2234</v>
       </c>
       <c r="E129" t="n">
         <v>60</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>WB арт.629086506</t>
+          <t>WB арт.486141710</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1057</v>
+        <v>1117</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NOW L-Tyrosine 500 mg 120 капсул, L-Тирозин</t>
+          <t>Easy Magic L-Тирозин 500 мг, 60 капсул, для мозга и тонуса</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D130" t="n">
-        <v>1103</v>
+        <v>825</v>
       </c>
       <c r="E130" t="n">
         <v>60</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>WB арт.577311165</t>
+          <t>WB арт.612963353</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>552</v>
+        <v>825</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Эвалар L тирозин 500 мг, L-tyrosine, 120 таблеток</t>
+          <t>NOW L Тирозин, для похудения и энергии 500 мг 120 шт</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>120</v>
       </c>
       <c r="D131" t="n">
-        <v>1457</v>
+        <v>750</v>
       </c>
       <c r="E131" t="n">
         <v>60</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>WB арт.322358421</t>
+          <t>WB арт.494022303</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>728</v>
+        <v>375</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -5536,26 +5536,26 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Тирозин</t>
+          <t>Таурин</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SOLGAR L-тирозин 500 мг 50шт</t>
+          <t>ВИТАМИР Витамир Таурин 500 таблетки массой 900 мг 30 шт</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D132" t="n">
-        <v>2130</v>
+        <v>235</v>
       </c>
       <c r="E132" t="n">
         <v>60</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>WB арт.258033150</t>
+          <t>WB арт.822676627</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5564,37 +5564,37 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2556</v>
+        <v>470</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Тирозин</t>
+          <t>Таурин</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SNT Тирозин L-TYROSINE 500 мг 60 капс</t>
+          <t>ВИТАМИР Витамир Таурин 1000 таблетки покрыт.об. массой 1545 мг 30 шт</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D133" t="n">
-        <v>1792</v>
+        <v>263</v>
       </c>
       <c r="E133" t="n">
         <v>60</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>WB арт.198623200</t>
+          <t>WB арт.822659120</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5603,37 +5603,37 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1792</v>
+        <v>526</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Тирозин</t>
+          <t>Таурин</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Doctor's BEST Тирозин L-Tyrosine 500 мг для похудения, от стресса 120 caps</t>
+          <t>NOW NUTRITION Таурин 1000 мг (Taurine 1000 mg), 100 капсул</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D134" t="n">
-        <v>2234</v>
+        <v>594</v>
       </c>
       <c r="E134" t="n">
         <v>60</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>WB арт.486141710</t>
+          <t>WB арт.445691558</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5642,37 +5642,37 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1117</v>
+        <v>356</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Тирозин</t>
+          <t>Таурин</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Easy Magic L-Тирозин 500 мг, 60 капсул, для мозга и тонуса</t>
+          <t>Life extension Taurine 1000мг 90 капсул Таурин 1000мг</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D135" t="n">
-        <v>825</v>
+        <v>1024</v>
       </c>
       <c r="E135" t="n">
         <v>60</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>WB арт.612963353</t>
+          <t>WB арт.378498824</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5681,37 +5681,37 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>825</v>
+        <v>683</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Тирозин</t>
+          <t>Таурин</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NOW L Тирозин, для похудения и энергии 500 мг 120 шт</t>
+          <t>Life extension Taurine, Таурин 1000 мг, 90 капсул</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D136" t="n">
-        <v>750</v>
+        <v>1650</v>
       </c>
       <c r="E136" t="n">
         <v>60</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>WB арт.494022303</t>
+          <t>WB арт.161900984</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5720,37 +5720,37 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>375</v>
+        <v>1100</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CoQ10</t>
+          <t>Таурин</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Турамин Турамин Коэнзим Q10 капсулы массой 0,5 г 60 шт</t>
+          <t>Эвалар Таурин Эвалар 1000 мг таблетки по 1,3 г 60 шт</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>60</v>
       </c>
       <c r="D137" t="n">
-        <v>712</v>
+        <v>899</v>
       </c>
       <c r="E137" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>WB арт.822662943</t>
+          <t>WB арт.822684608</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5759,37 +5759,37 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>356</v>
+        <v>899</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CoQ10</t>
+          <t>Таурин</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NOW CoQ10 CoQ-10 100 mg Коэнзим q10 - 50 капсул</t>
+          <t>aTech nutrition БАД Аминокислота Таурин энерджи 1200 мг 60 капсул</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D138" t="n">
-        <v>595</v>
+        <v>263</v>
       </c>
       <c r="E138" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>WB арт.355561105</t>
+          <t>WB арт.17028481</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5798,11 +5798,11 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>357</v>
+        <v>263</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -5814,21 +5814,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VivaForte Коэнзим Q10 120 капсул для кожи и волос 100 мг</t>
+          <t>Турамин Турамин Коэнзим Q10 капсулы массой 0,5 г 60 шт</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D139" t="n">
-        <v>385</v>
+        <v>712</v>
       </c>
       <c r="E139" t="n">
         <v>30</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>WB арт.385564545</t>
+          <t>WB арт.822662943</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>96</v>
+        <v>356</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GLS pharmaceuticals Коэнзим Q10 GLS капсулы по 310 мг 60 шт</t>
+          <t>NOW CoQ10 CoQ-10 100 mg Коэнзим q10 - 50 капсул</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D140" t="n">
-        <v>481</v>
+        <v>595</v>
       </c>
       <c r="E140" t="n">
         <v>30</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>WB арт.822663219</t>
+          <t>WB арт.355561105</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5876,11 +5876,11 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>241</v>
+        <v>357</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -5892,21 +5892,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Энерго Био Системы Коэнзим q10 100 мг 60 капсул</t>
+          <t>VivaForte Коэнзим Q10 120 капсул для кожи и волос 100 мг</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D141" t="n">
-        <v>780</v>
+        <v>385</v>
       </c>
       <c r="E141" t="n">
         <v>30</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>WB арт.998280723</t>
+          <t>WB арт.385564545</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5915,11 +5915,11 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>390</v>
+        <v>96</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -5931,21 +5931,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vitality of nature Vitality Коэнзим Q-10 60 капсул</t>
+          <t>GLS pharmaceuticals Коэнзим Q10 GLS капсулы по 310 мг 60 шт</t>
         </is>
       </c>
       <c r="C142" t="n">
         <v>60</v>
       </c>
       <c r="D142" t="n">
-        <v>1656</v>
+        <v>481</v>
       </c>
       <c r="E142" t="n">
         <v>30</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>WB арт.969065678</t>
+          <t>WB арт.822663219</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5954,11 +5954,11 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>828</v>
+        <v>241</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -5970,21 +5970,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ВИТАМИР Красный дрожжевой рис и коэнзим Q10 30 капс</t>
+          <t>Энерго Био Системы Коэнзим q10 100 мг 60 капсул</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D143" t="n">
-        <v>901</v>
+        <v>780</v>
       </c>
       <c r="E143" t="n">
         <v>30</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>WB арт.45347588</t>
+          <t>WB арт.998280723</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5993,37 +5993,37 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>901</v>
+        <v>390</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Пикногенол</t>
+          <t>CoQ10</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Витамины пикногенол Pycnogenol Strong, 60 шт</t>
+          <t>Vitality of nature Vitality Коэнзим Q-10 60 капсул</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>60</v>
       </c>
       <c r="D144" t="n">
-        <v>2566</v>
+        <v>1656</v>
       </c>
       <c r="E144" t="n">
         <v>30</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>WB арт.851658801</t>
+          <t>WB арт.969065678</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6032,37 +6032,37 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1283</v>
+        <v>828</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Пикногенол</t>
+          <t>CoQ10</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NOW Pycnogenol 100 mg, Пикногенол, 60 капсул</t>
+          <t>ВИТАМИР Красный дрожжевой рис и коэнзим Q10 30 капс</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D145" t="n">
-        <v>8672</v>
+        <v>901</v>
       </c>
       <c r="E145" t="n">
         <v>30</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>WB арт.420923240</t>
+          <t>WB арт.45347588</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>4336</v>
+        <v>901</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>swanson Пикногенол, 100 мг, 30 капсул</t>
+          <t xml:space="preserve"> Витамины пикногенол Pycnogenol Strong, 60 шт</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D146" t="n">
-        <v>6418</v>
+        <v>2566</v>
       </c>
       <c r="E146" t="n">
         <v>30</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>WB арт.187627381</t>
+          <t>WB арт.851658801</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6110,11 +6110,11 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>6418</v>
+        <v>1283</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -6126,21 +6126,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пикногенол Стронг Pycnogenol Strong (40 mg), 60 таб - 2 упак…</t>
+          <t>NOW Pycnogenol 100 mg, Пикногенол, 60 капсул</t>
         </is>
       </c>
       <c r="C147" t="n">
         <v>60</v>
       </c>
       <c r="D147" t="n">
-        <v>4309</v>
+        <v>8672</v>
       </c>
       <c r="E147" t="n">
         <v>30</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>WB арт.840532524</t>
+          <t>WB арт.420923240</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6149,11 +6149,11 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>2154</v>
+        <v>4336</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -6165,21 +6165,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>без бренда Капилар таблетки 100 шт</t>
+          <t>swanson Пикногенол, 100 мг, 30 капсул</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D148" t="n">
-        <v>605</v>
+        <v>6418</v>
       </c>
       <c r="E148" t="n">
         <v>30</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>WB арт.161219831</t>
+          <t>WB арт.187627381</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6188,11 +6188,11 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>182</v>
+        <v>6418</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -6204,21 +6204,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пикногенол Стронг Pycnogenol Strong (40 mg), 60 таб</t>
+          <t xml:space="preserve"> Пикногенол Стронг Pycnogenol Strong (40 mg), 60 таб - 2 упак…</t>
         </is>
       </c>
       <c r="C149" t="n">
         <v>60</v>
       </c>
       <c r="D149" t="n">
-        <v>2520</v>
+        <v>4309</v>
       </c>
       <c r="E149" t="n">
         <v>30</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>WB арт.494529733</t>
+          <t>WB арт.840532524</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6227,11 +6227,11 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1260</v>
+        <v>2154</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -6243,21 +6243,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Source Naturals Пикногенол Supreme, 60 таблеток</t>
+          <t>без бренда Капилар таблетки 100 шт</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D150" t="n">
-        <v>5379</v>
+        <v>605</v>
       </c>
       <c r="E150" t="n">
         <v>30</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>WB арт.1379669962</t>
+          <t>WB арт.161219831</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6266,11 +6266,11 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>2690</v>
+        <v>182</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -6282,21 +6282,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Life Extension Пикногенол 100 мг, 60 капсул</t>
+          <t xml:space="preserve"> Пикногенол Стронг Pycnogenol Strong (40 mg), 60 таб</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>60</v>
       </c>
       <c r="D151" t="n">
-        <v>2103</v>
+        <v>2520</v>
       </c>
       <c r="E151" t="n">
         <v>30</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>WB арт.1497793308</t>
+          <t>WB арт.494529733</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1052</v>
+        <v>1260</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -6316,26 +6316,26 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Готу кола</t>
+          <t>Пикногенол</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NOW Gotu Kola Готу Кола, Центелла Азиатская 450 мг - 100 капсул</t>
+          <t>Source Naturals Пикногенол Supreme, 60 таблеток</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D152" t="n">
-        <v>1026</v>
+        <v>5379</v>
       </c>
       <c r="E152" t="n">
         <v>30</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>WB арт.139223570</t>
+          <t>WB арт.1379669962</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6344,37 +6344,37 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>308</v>
+        <v>2690</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Готу кола</t>
+          <t>Пикногенол</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OVER Глицин + Гинкго Билоба + Готу Кола, 60 капсул</t>
+          <t xml:space="preserve"> Life Extension Пикногенол 100 мг, 60 капсул</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>60</v>
       </c>
       <c r="D153" t="n">
-        <v>674</v>
+        <v>2103</v>
       </c>
       <c r="E153" t="n">
         <v>30</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>WB арт.167807321</t>
+          <t>WB арт.1497793308</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6383,11 +6383,11 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>337</v>
+        <v>1052</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -6399,21 +6399,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Alantra Готу Кола капсулы Алантра, 500 мг*60 шт</t>
+          <t>NOW Gotu Kola Готу Кола, Центелла Азиатская 450 мг - 100 капсул</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D154" t="n">
-        <v>961</v>
+        <v>1026</v>
       </c>
       <c r="E154" t="n">
         <v>30</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>WB арт.978377015</t>
+          <t>WB арт.139223570</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6422,11 +6422,11 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>480</v>
+        <v>308</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -6438,21 +6438,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NOW Gotu Kola Готу Кола, Центелла Азиатская 450 мг - 100 капсул</t>
+          <t>OVER Глицин + Гинкго Билоба + Готу Кола, 60 капсул</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D155" t="n">
-        <v>1046</v>
+        <v>674</v>
       </c>
       <c r="E155" t="n">
         <v>30</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>WB арт.138748103</t>
+          <t>WB арт.167807321</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6461,11 +6461,11 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
@@ -6477,21 +6477,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nature's way Готу Кола 100 капсул</t>
+          <t>Alantra Готу Кола капсулы Алантра, 500 мг*60 шт</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D156" t="n">
-        <v>2455</v>
+        <v>961</v>
       </c>
       <c r="E156" t="n">
         <v>30</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>WB арт.447867459</t>
+          <t>WB арт.978377015</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>736</v>
+        <v>480</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Shri Ganga Для памяти и улучшения слуха Гото Кула Goto Kula 100 таб</t>
+          <t>NOW Gotu Kola Готу Кола, Центелла Азиатская 450 мг - 100 капсул</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>100</v>
       </c>
       <c r="D157" t="n">
-        <v>473</v>
+        <v>1046</v>
       </c>
       <c r="E157" t="n">
         <v>30</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>WB арт.924661260</t>
+          <t>WB арт.138748103</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>142</v>
+        <v>314</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -6555,32 +6555,110 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
+          <t>Nature's way Готу Кола 100 капсул</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>100</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2455</v>
+      </c>
+      <c r="E158" t="n">
+        <v>30</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>WB арт.447867459</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>736</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Готу кола</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Shri Ganga Для памяти и улучшения слуха Гото Кула Goto Kula 100 таб</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>100</v>
+      </c>
+      <c r="D159" t="n">
+        <v>473</v>
+      </c>
+      <c r="E159" t="n">
+        <v>30</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>WB арт.924661260</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>142</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Готу кола</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
           <t>GLS pharmaceuticals Гинкго билоба+Готу кола GLS капсулы по 380 мг 60 шт</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>60</v>
-      </c>
-      <c r="D158" t="n">
+      <c r="C160" t="n">
+        <v>60</v>
+      </c>
+      <c r="D160" t="n">
         <v>727</v>
       </c>
-      <c r="E158" t="n">
-        <v>30</v>
-      </c>
-      <c r="F158" t="inlineStr">
+      <c r="E160" t="n">
+        <v>30</v>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>WB арт.822682995</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="H158" t="n">
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
         <v>364</v>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t>средний</t>
         </is>

--- a/data/raw/prices_wb.xlsx
+++ b/data/raw/prices_wb.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I160"/>
+  <dimension ref="A1:I169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6438,21 +6438,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OVER Глицин + Гинкго Билоба + Готу Кола, 60 капсул</t>
+          <t>Alantra Готу Кола капсулы Алантра, 500 мг*60 шт</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>60</v>
       </c>
       <c r="D155" t="n">
-        <v>674</v>
+        <v>961</v>
       </c>
       <c r="E155" t="n">
         <v>30</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>WB арт.167807321</t>
+          <t>WB арт.978377015</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6461,11 +6461,11 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>337</v>
+        <v>480</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>средний</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -6477,21 +6477,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Alantra Готу Кола капсулы Алантра, 500 мг*60 шт</t>
+          <t>NOW Gotu Kola Готу Кола, Центелла Азиатская 450 мг - 100 капсул</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D156" t="n">
-        <v>961</v>
+        <v>1046</v>
       </c>
       <c r="E156" t="n">
         <v>30</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>WB арт.978377015</t>
+          <t>WB арт.138748103</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6500,11 +6500,11 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>480</v>
+        <v>314</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -6516,21 +6516,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NOW Gotu Kola Готу Кола, Центелла Азиатская 450 мг - 100 капсул</t>
+          <t>Nature's way Готу Кола 100 капсул</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>100</v>
       </c>
       <c r="D157" t="n">
-        <v>1046</v>
+        <v>2455</v>
       </c>
       <c r="E157" t="n">
         <v>30</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>WB арт.138748103</t>
+          <t>WB арт.447867459</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6539,11 +6539,11 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>314</v>
+        <v>736</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>премиум</t>
         </is>
       </c>
     </row>
@@ -6555,21 +6555,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Nature's way Готу Кола 100 капсул</t>
+          <t>Shri Ganga Для памяти и улучшения слуха Гото Кула Goto Kula 100 таб</t>
         </is>
       </c>
       <c r="C158" t="n">
         <v>100</v>
       </c>
       <c r="D158" t="n">
-        <v>2455</v>
+        <v>473</v>
       </c>
       <c r="E158" t="n">
         <v>30</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>WB арт.447867459</t>
+          <t>WB арт.924661260</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6578,11 +6578,11 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>736</v>
+        <v>142</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>эконом</t>
         </is>
       </c>
     </row>
@@ -6594,21 +6594,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Shri Ganga Для памяти и улучшения слуха Гото Кула Goto Kula 100 таб</t>
+          <t>GLS pharmaceuticals Гинкго билоба+Готу кола GLS капсулы по 380 мг 60 шт</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D159" t="n">
-        <v>473</v>
+        <v>727</v>
       </c>
       <c r="E159" t="n">
         <v>30</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>WB арт.924661260</t>
+          <t>WB арт.822682995</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6617,37 +6617,37 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>142</v>
+        <v>364</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>средний</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Готу кола</t>
+          <t>Креатин</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GLS pharmaceuticals Гинкго билоба+Готу кола GLS капсулы по 380 мг 60 шт</t>
+          <t>Prime Kraft Креатин моногидрат Creatine Monohydrate, без вкуса 200 гр</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="D160" t="n">
-        <v>727</v>
+        <v>640</v>
       </c>
       <c r="E160" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>WB арт.822682995</t>
+          <t>WB арт.4219394</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6656,13 +6656,324 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>364</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>средний</t>
-        </is>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="I160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Prime Kraft Креатин Creatine Monohydrate 100% Pure (без вкуса), 500 гр</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>500</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1411</v>
+      </c>
+      <c r="E161" t="n">
+        <v>150</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>WB арт.13257465</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>423</v>
+      </c>
+      <c r="I161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Prime Kraft Креатин Creatine Monohydrate, Вишня 200 гр</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>200</v>
+      </c>
+      <c r="D162" t="n">
+        <v>660</v>
+      </c>
+      <c r="E162" t="n">
+        <v>150</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>WB арт.120930475</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>495</v>
+      </c>
+      <c r="I162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Prime Kraft Креатин Creatine Monohydrate, Энергетик 200 гр</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>200</v>
+      </c>
+      <c r="D163" t="n">
+        <v>660</v>
+      </c>
+      <c r="E163" t="n">
+        <v>150</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>WB арт.228766204</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>495</v>
+      </c>
+      <c r="I163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Prime Kraft Креатин Creatine Monohydrate, Ананас 200 гр</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>200</v>
+      </c>
+      <c r="D164" t="n">
+        <v>845</v>
+      </c>
+      <c r="E164" t="n">
+        <v>150</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>WB арт.120930473</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>634</v>
+      </c>
+      <c r="I164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Prime Kraft Креатин Creatine Monohydrate, Цитрусовый микс 200 гр</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>200</v>
+      </c>
+      <c r="D165" t="n">
+        <v>563</v>
+      </c>
+      <c r="E165" t="n">
+        <v>150</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>WB арт.120930474</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>422</v>
+      </c>
+      <c r="I165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Prime Kraft Креатин Creatine Monohydrate, Вишня 500 гр</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>500</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1525</v>
+      </c>
+      <c r="E166" t="n">
+        <v>150</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>WB арт.183766036</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>458</v>
+      </c>
+      <c r="I166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Prime Kraft Креатин Creatine Monohydrate Pineapple (ананас), 500 гр</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>500</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1490</v>
+      </c>
+      <c r="E167" t="n">
+        <v>150</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>WB арт.183766034</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>447</v>
+      </c>
+      <c r="I167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>BIOVIN Креатин моногидрат порошок, спортивное питание creatine 300г</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>300</v>
+      </c>
+      <c r="D168" t="n">
+        <v>385</v>
+      </c>
+      <c r="E168" t="n">
+        <v>150</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>WB арт.59102656</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>193</v>
+      </c>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Креатин</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Prime Kraft Креатин моногидрат микронизированный, фруктовый пунш 200 гр</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>200</v>
+      </c>
+      <c r="D169" t="n">
+        <v>668</v>
+      </c>
+      <c r="E169" t="n">
+        <v>150</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>WB арт.213577274</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>501</v>
+      </c>
+      <c r="I169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/prices_wb.xlsx
+++ b/data/raw/prices_wb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\analytics\brain-25-evidence\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D7D3F5-06F5-4300-8D78-10B5CD42AD6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C446CF9-8270-4A34-8C70-AB5318F4B949}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="364">
   <si>
     <t>добавка</t>
   </si>
@@ -467,12 +467,6 @@
   </si>
   <si>
     <t>WB арт.822680108</t>
-  </si>
-  <si>
-    <t>– Родиолы экстракт жидкий для приема внутрь 30 мл 1 шт</t>
-  </si>
-  <si>
-    <t>WB арт.822684736</t>
   </si>
   <si>
     <t>эколаб Родиола + витамин С 90 капсул</t>
@@ -1457,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I168"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3324,10 +3318,10 @@
         <v>149</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="D65">
-        <v>140</v>
+        <v>604</v>
       </c>
       <c r="E65">
         <v>30</v>
@@ -3339,36 +3333,36 @@
         <v>12</v>
       </c>
       <c r="H65">
-        <v>4200</v>
+        <v>201</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C66">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D66">
-        <v>604</v>
+        <v>1839</v>
       </c>
       <c r="E66">
         <v>30</v>
       </c>
       <c r="F66" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G66" t="s">
         <v>12</v>
       </c>
       <c r="H66">
-        <v>201</v>
+        <v>920</v>
       </c>
       <c r="I66" t="s">
         <v>13</v>
@@ -3376,7 +3370,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B67" t="s">
         <v>154</v>
@@ -3385,7 +3379,7 @@
         <v>60</v>
       </c>
       <c r="D67">
-        <v>1839</v>
+        <v>2586</v>
       </c>
       <c r="E67">
         <v>30</v>
@@ -3397,15 +3391,15 @@
         <v>12</v>
       </c>
       <c r="H67">
-        <v>920</v>
+        <v>1293</v>
       </c>
       <c r="I67" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B68" t="s">
         <v>156</v>
@@ -3414,7 +3408,7 @@
         <v>60</v>
       </c>
       <c r="D68">
-        <v>2586</v>
+        <v>2799</v>
       </c>
       <c r="E68">
         <v>30</v>
@@ -3426,7 +3420,7 @@
         <v>12</v>
       </c>
       <c r="H68">
-        <v>1293</v>
+        <v>1400</v>
       </c>
       <c r="I68" t="s">
         <v>16</v>
@@ -3434,16 +3428,16 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B69" t="s">
         <v>158</v>
       </c>
       <c r="C69">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D69">
-        <v>2799</v>
+        <v>1994</v>
       </c>
       <c r="E69">
         <v>30</v>
@@ -3455,24 +3449,24 @@
         <v>12</v>
       </c>
       <c r="H69">
-        <v>1400</v>
+        <v>1994</v>
       </c>
       <c r="I69" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B70" t="s">
         <v>160</v>
       </c>
       <c r="C70">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D70">
-        <v>1994</v>
+        <v>4198</v>
       </c>
       <c r="E70">
         <v>30</v>
@@ -3484,7 +3478,7 @@
         <v>12</v>
       </c>
       <c r="H70">
-        <v>1994</v>
+        <v>2099</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
@@ -3492,16 +3486,16 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B71" t="s">
         <v>162</v>
       </c>
       <c r="C71">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D71">
-        <v>4198</v>
+        <v>4654</v>
       </c>
       <c r="E71">
         <v>30</v>
@@ -3513,24 +3507,24 @@
         <v>12</v>
       </c>
       <c r="H71">
-        <v>2099</v>
+        <v>1164</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B72" t="s">
         <v>164</v>
       </c>
       <c r="C72">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D72">
-        <v>4654</v>
+        <v>4365</v>
       </c>
       <c r="E72">
         <v>30</v>
@@ -3542,24 +3536,24 @@
         <v>12</v>
       </c>
       <c r="H72">
-        <v>1164</v>
+        <v>2182</v>
       </c>
       <c r="I72" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B73" t="s">
         <v>166</v>
       </c>
       <c r="C73">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D73">
-        <v>4365</v>
+        <v>2799</v>
       </c>
       <c r="E73">
         <v>30</v>
@@ -3571,53 +3565,53 @@
         <v>12</v>
       </c>
       <c r="H73">
-        <v>2182</v>
+        <v>700</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C74">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D74">
-        <v>2799</v>
+        <v>2818</v>
       </c>
       <c r="E74">
         <v>30</v>
       </c>
       <c r="F74" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G74" t="s">
         <v>12</v>
       </c>
       <c r="H74">
-        <v>700</v>
+        <v>1409</v>
       </c>
       <c r="I74" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B75" t="s">
         <v>171</v>
       </c>
       <c r="C75">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D75">
-        <v>2818</v>
+        <v>3868</v>
       </c>
       <c r="E75">
         <v>30</v>
@@ -3629,24 +3623,24 @@
         <v>12</v>
       </c>
       <c r="H75">
-        <v>1409</v>
+        <v>1289</v>
       </c>
       <c r="I75" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B76" t="s">
         <v>173</v>
       </c>
       <c r="C76">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D76">
-        <v>3868</v>
+        <v>3498</v>
       </c>
       <c r="E76">
         <v>30</v>
@@ -3658,15 +3652,15 @@
         <v>12</v>
       </c>
       <c r="H76">
-        <v>1289</v>
+        <v>1749</v>
       </c>
       <c r="I76" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B77" t="s">
         <v>175</v>
@@ -3675,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="D77">
-        <v>3498</v>
+        <v>1517</v>
       </c>
       <c r="E77">
         <v>30</v>
@@ -3687,15 +3681,15 @@
         <v>12</v>
       </c>
       <c r="H77">
-        <v>1749</v>
+        <v>758</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
         <v>177</v>
@@ -3704,7 +3698,7 @@
         <v>60</v>
       </c>
       <c r="D78">
-        <v>1517</v>
+        <v>2970</v>
       </c>
       <c r="E78">
         <v>30</v>
@@ -3716,15 +3710,15 @@
         <v>12</v>
       </c>
       <c r="H78">
-        <v>758</v>
+        <v>1485</v>
       </c>
       <c r="I78" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B79" t="s">
         <v>179</v>
@@ -3733,7 +3727,7 @@
         <v>60</v>
       </c>
       <c r="D79">
-        <v>2970</v>
+        <v>1584</v>
       </c>
       <c r="E79">
         <v>30</v>
@@ -3745,24 +3739,24 @@
         <v>12</v>
       </c>
       <c r="H79">
-        <v>1485</v>
+        <v>792</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
         <v>181</v>
       </c>
       <c r="C80">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D80">
-        <v>1584</v>
+        <v>3947</v>
       </c>
       <c r="E80">
         <v>30</v>
@@ -3774,53 +3768,53 @@
         <v>12</v>
       </c>
       <c r="H80">
-        <v>792</v>
+        <v>1316</v>
       </c>
       <c r="I80" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B81" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C81">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D81">
-        <v>3947</v>
+        <v>1824</v>
       </c>
       <c r="E81">
         <v>30</v>
       </c>
       <c r="F81" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G81" t="s">
         <v>12</v>
       </c>
       <c r="H81">
-        <v>1316</v>
+        <v>5472</v>
       </c>
       <c r="I81" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B82" t="s">
         <v>186</v>
       </c>
       <c r="C82">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D82">
-        <v>1824</v>
+        <v>271</v>
       </c>
       <c r="E82">
         <v>30</v>
@@ -3832,24 +3826,24 @@
         <v>12</v>
       </c>
       <c r="H82">
-        <v>5472</v>
+        <v>1626</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B83" t="s">
         <v>188</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D83">
-        <v>271</v>
+        <v>3714</v>
       </c>
       <c r="E83">
         <v>30</v>
@@ -3861,44 +3855,44 @@
         <v>12</v>
       </c>
       <c r="H83">
-        <v>1626</v>
+        <v>1857</v>
       </c>
       <c r="I83" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B84" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C84">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D84">
-        <v>3714</v>
+        <v>3667</v>
       </c>
       <c r="E84">
         <v>30</v>
       </c>
       <c r="F84" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G84" t="s">
         <v>12</v>
       </c>
       <c r="H84">
-        <v>1857</v>
+        <v>917</v>
       </c>
       <c r="I84" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B85" t="s">
         <v>193</v>
@@ -3907,7 +3901,7 @@
         <v>120</v>
       </c>
       <c r="D85">
-        <v>3667</v>
+        <v>3949</v>
       </c>
       <c r="E85">
         <v>30</v>
@@ -3919,24 +3913,24 @@
         <v>12</v>
       </c>
       <c r="H85">
-        <v>917</v>
+        <v>987</v>
       </c>
       <c r="I85" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B86" t="s">
         <v>195</v>
       </c>
       <c r="C86">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="D86">
-        <v>3949</v>
+        <v>11280</v>
       </c>
       <c r="E86">
         <v>30</v>
@@ -3948,24 +3942,24 @@
         <v>12</v>
       </c>
       <c r="H86">
-        <v>987</v>
+        <v>1410</v>
       </c>
       <c r="I86" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B87" t="s">
         <v>197</v>
       </c>
       <c r="C87">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="D87">
-        <v>11280</v>
+        <v>4229</v>
       </c>
       <c r="E87">
         <v>30</v>
@@ -3977,7 +3971,7 @@
         <v>12</v>
       </c>
       <c r="H87">
-        <v>1410</v>
+        <v>1057</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
@@ -3985,16 +3979,16 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B88" t="s">
         <v>199</v>
       </c>
       <c r="C88">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="D88">
-        <v>4229</v>
+        <v>4088</v>
       </c>
       <c r="E88">
         <v>30</v>
@@ -4006,82 +4000,82 @@
         <v>12</v>
       </c>
       <c r="H88">
-        <v>1057</v>
+        <v>511</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B89" t="s">
+        <v>197</v>
+      </c>
+      <c r="C89">
+        <v>120</v>
+      </c>
+      <c r="D89">
+        <v>3722</v>
+      </c>
+      <c r="E89">
+        <v>30</v>
+      </c>
+      <c r="F89" t="s">
         <v>201</v>
       </c>
-      <c r="C89">
-        <v>240</v>
-      </c>
-      <c r="D89">
-        <v>4088</v>
-      </c>
-      <c r="E89">
-        <v>30</v>
-      </c>
-      <c r="F89" t="s">
-        <v>202</v>
-      </c>
       <c r="G89" t="s">
         <v>12</v>
       </c>
       <c r="H89">
-        <v>511</v>
+        <v>930</v>
       </c>
       <c r="I89" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B90" t="s">
         <v>199</v>
       </c>
       <c r="C90">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="D90">
-        <v>3722</v>
+        <v>4051</v>
       </c>
       <c r="E90">
         <v>30</v>
       </c>
       <c r="F90" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G90" t="s">
         <v>12</v>
       </c>
       <c r="H90">
-        <v>930</v>
+        <v>506</v>
       </c>
       <c r="I90" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B91" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C91">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="D91">
-        <v>4051</v>
+        <v>2295</v>
       </c>
       <c r="E91">
         <v>30</v>
@@ -4093,36 +4087,36 @@
         <v>12</v>
       </c>
       <c r="H91">
-        <v>506</v>
+        <v>1148</v>
       </c>
       <c r="I91" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B92" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C92">
         <v>60</v>
       </c>
       <c r="D92">
-        <v>2295</v>
+        <v>1683</v>
       </c>
       <c r="E92">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F92" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G92" t="s">
         <v>12</v>
       </c>
       <c r="H92">
-        <v>1148</v>
+        <v>1683</v>
       </c>
       <c r="I92" t="s">
         <v>19</v>
@@ -4130,7 +4124,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B93" t="s">
         <v>208</v>
@@ -4139,7 +4133,7 @@
         <v>60</v>
       </c>
       <c r="D93">
-        <v>1683</v>
+        <v>467</v>
       </c>
       <c r="E93">
         <v>60</v>
@@ -4151,15 +4145,15 @@
         <v>12</v>
       </c>
       <c r="H93">
-        <v>1683</v>
+        <v>467</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B94" t="s">
         <v>210</v>
@@ -4168,7 +4162,7 @@
         <v>60</v>
       </c>
       <c r="D94">
-        <v>467</v>
+        <v>342</v>
       </c>
       <c r="E94">
         <v>60</v>
@@ -4180,7 +4174,7 @@
         <v>12</v>
       </c>
       <c r="H94">
-        <v>467</v>
+        <v>342</v>
       </c>
       <c r="I94" t="s">
         <v>13</v>
@@ -4188,7 +4182,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B95" t="s">
         <v>212</v>
@@ -4197,7 +4191,7 @@
         <v>60</v>
       </c>
       <c r="D95">
-        <v>342</v>
+        <v>750</v>
       </c>
       <c r="E95">
         <v>60</v>
@@ -4209,24 +4203,24 @@
         <v>12</v>
       </c>
       <c r="H95">
-        <v>342</v>
+        <v>750</v>
       </c>
       <c r="I95" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B96" t="s">
         <v>214</v>
       </c>
       <c r="C96">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D96">
-        <v>750</v>
+        <v>679</v>
       </c>
       <c r="E96">
         <v>60</v>
@@ -4238,24 +4232,24 @@
         <v>12</v>
       </c>
       <c r="H96">
-        <v>750</v>
+        <v>340</v>
       </c>
       <c r="I96" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B97" t="s">
         <v>216</v>
       </c>
       <c r="C97">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D97">
-        <v>679</v>
+        <v>2553</v>
       </c>
       <c r="E97">
         <v>60</v>
@@ -4267,24 +4261,24 @@
         <v>12</v>
       </c>
       <c r="H97">
-        <v>340</v>
+        <v>5106</v>
       </c>
       <c r="I97" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B98" t="s">
         <v>218</v>
       </c>
       <c r="C98">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D98">
-        <v>2553</v>
+        <v>820</v>
       </c>
       <c r="E98">
         <v>60</v>
@@ -4296,24 +4290,24 @@
         <v>12</v>
       </c>
       <c r="H98">
-        <v>5106</v>
+        <v>820</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B99" t="s">
         <v>220</v>
       </c>
       <c r="C99">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D99">
-        <v>820</v>
+        <v>681</v>
       </c>
       <c r="E99">
         <v>60</v>
@@ -4325,15 +4319,15 @@
         <v>12</v>
       </c>
       <c r="H99">
-        <v>820</v>
+        <v>1362</v>
       </c>
       <c r="I99" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B100" t="s">
         <v>222</v>
@@ -4342,7 +4336,7 @@
         <v>30</v>
       </c>
       <c r="D100">
-        <v>681</v>
+        <v>606</v>
       </c>
       <c r="E100">
         <v>60</v>
@@ -4354,44 +4348,44 @@
         <v>12</v>
       </c>
       <c r="H100">
-        <v>1362</v>
+        <v>1212</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B101" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C101">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D101">
-        <v>606</v>
+        <v>812</v>
       </c>
       <c r="E101">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F101" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>12</v>
       </c>
       <c r="H101">
-        <v>1212</v>
+        <v>406</v>
       </c>
       <c r="I101" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B102" t="s">
         <v>227</v>
@@ -4400,7 +4394,7 @@
         <v>60</v>
       </c>
       <c r="D102">
-        <v>812</v>
+        <v>245</v>
       </c>
       <c r="E102">
         <v>30</v>
@@ -4412,7 +4406,7 @@
         <v>12</v>
       </c>
       <c r="H102">
-        <v>406</v>
+        <v>122</v>
       </c>
       <c r="I102" t="s">
         <v>13</v>
@@ -4420,16 +4414,16 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B103" t="s">
         <v>229</v>
       </c>
       <c r="C103">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D103">
-        <v>245</v>
+        <v>1062</v>
       </c>
       <c r="E103">
         <v>30</v>
@@ -4441,7 +4435,7 @@
         <v>12</v>
       </c>
       <c r="H103">
-        <v>122</v>
+        <v>354</v>
       </c>
       <c r="I103" t="s">
         <v>13</v>
@@ -4449,16 +4443,16 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B104" t="s">
         <v>231</v>
       </c>
       <c r="C104">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D104">
-        <v>1062</v>
+        <v>1584</v>
       </c>
       <c r="E104">
         <v>30</v>
@@ -4470,15 +4464,15 @@
         <v>12</v>
       </c>
       <c r="H104">
-        <v>354</v>
+        <v>792</v>
       </c>
       <c r="I104" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B105" t="s">
         <v>233</v>
@@ -4487,7 +4481,7 @@
         <v>60</v>
       </c>
       <c r="D105">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="E105">
         <v>30</v>
@@ -4507,7 +4501,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B106" t="s">
         <v>235</v>
@@ -4516,7 +4510,7 @@
         <v>60</v>
       </c>
       <c r="D106">
-        <v>1585</v>
+        <v>1722</v>
       </c>
       <c r="E106">
         <v>30</v>
@@ -4528,53 +4522,53 @@
         <v>12</v>
       </c>
       <c r="H106">
-        <v>792</v>
+        <v>861</v>
       </c>
       <c r="I106" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B107" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C107">
         <v>60</v>
       </c>
       <c r="D107">
-        <v>1722</v>
+        <v>973</v>
       </c>
       <c r="E107">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F107" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G107" t="s">
         <v>12</v>
       </c>
       <c r="H107">
-        <v>861</v>
+        <v>973</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B108" t="s">
         <v>240</v>
       </c>
       <c r="C108">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D108">
-        <v>973</v>
+        <v>1278</v>
       </c>
       <c r="E108">
         <v>60</v>
@@ -4586,7 +4580,7 @@
         <v>12</v>
       </c>
       <c r="H108">
-        <v>973</v>
+        <v>852</v>
       </c>
       <c r="I108" t="s">
         <v>13</v>
@@ -4594,16 +4588,16 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B109" t="s">
         <v>242</v>
       </c>
       <c r="C109">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D109">
-        <v>1278</v>
+        <v>1428</v>
       </c>
       <c r="E109">
         <v>60</v>
@@ -4615,15 +4609,15 @@
         <v>12</v>
       </c>
       <c r="H109">
-        <v>852</v>
+        <v>1428</v>
       </c>
       <c r="I109" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B110" t="s">
         <v>244</v>
@@ -4632,7 +4626,7 @@
         <v>60</v>
       </c>
       <c r="D110">
-        <v>1428</v>
+        <v>1527</v>
       </c>
       <c r="E110">
         <v>60</v>
@@ -4644,24 +4638,24 @@
         <v>12</v>
       </c>
       <c r="H110">
-        <v>1428</v>
+        <v>1527</v>
       </c>
       <c r="I110" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B111" t="s">
         <v>246</v>
       </c>
       <c r="C111">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D111">
-        <v>1527</v>
+        <v>1817</v>
       </c>
       <c r="E111">
         <v>60</v>
@@ -4673,53 +4667,53 @@
         <v>12</v>
       </c>
       <c r="H111">
-        <v>1527</v>
+        <v>1090</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B112" t="s">
+        <v>240</v>
+      </c>
+      <c r="C112">
+        <v>90</v>
+      </c>
+      <c r="D112">
+        <v>1222</v>
+      </c>
+      <c r="E112">
+        <v>60</v>
+      </c>
+      <c r="F112" t="s">
         <v>248</v>
       </c>
-      <c r="C112">
-        <v>100</v>
-      </c>
-      <c r="D112">
-        <v>1817</v>
-      </c>
-      <c r="E112">
-        <v>60</v>
-      </c>
-      <c r="F112" t="s">
-        <v>249</v>
-      </c>
       <c r="G112" t="s">
         <v>12</v>
       </c>
       <c r="H112">
-        <v>1090</v>
+        <v>815</v>
       </c>
       <c r="I112" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B113" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C113">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D113">
-        <v>1222</v>
+        <v>1587</v>
       </c>
       <c r="E113">
         <v>60</v>
@@ -4731,24 +4725,24 @@
         <v>12</v>
       </c>
       <c r="H113">
-        <v>815</v>
+        <v>1587</v>
       </c>
       <c r="I113" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B114" t="s">
         <v>251</v>
       </c>
       <c r="C114">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D114">
-        <v>1587</v>
+        <v>3667</v>
       </c>
       <c r="E114">
         <v>60</v>
@@ -4760,7 +4754,7 @@
         <v>12</v>
       </c>
       <c r="H114">
-        <v>1587</v>
+        <v>1834</v>
       </c>
       <c r="I114" t="s">
         <v>19</v>
@@ -4768,28 +4762,28 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B115" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C115">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D115">
-        <v>3667</v>
+        <v>1283</v>
       </c>
       <c r="E115">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F115" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G115" t="s">
         <v>12</v>
       </c>
       <c r="H115">
-        <v>1834</v>
+        <v>642</v>
       </c>
       <c r="I115" t="s">
         <v>19</v>
@@ -4797,16 +4791,16 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B116" t="s">
         <v>256</v>
       </c>
       <c r="C116">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D116">
-        <v>1283</v>
+        <v>848</v>
       </c>
       <c r="E116">
         <v>30</v>
@@ -4818,24 +4812,24 @@
         <v>12</v>
       </c>
       <c r="H116">
-        <v>642</v>
+        <v>283</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B117" t="s">
         <v>258</v>
       </c>
       <c r="C117">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D117">
-        <v>848</v>
+        <v>888</v>
       </c>
       <c r="E117">
         <v>30</v>
@@ -4847,24 +4841,24 @@
         <v>12</v>
       </c>
       <c r="H117">
-        <v>283</v>
+        <v>888</v>
       </c>
       <c r="I117" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B118" t="s">
         <v>260</v>
       </c>
       <c r="C118">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D118">
-        <v>888</v>
+        <v>409</v>
       </c>
       <c r="E118">
         <v>30</v>
@@ -4876,24 +4870,24 @@
         <v>12</v>
       </c>
       <c r="H118">
-        <v>888</v>
+        <v>102</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B119" t="s">
         <v>262</v>
       </c>
       <c r="C119">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D119">
-        <v>409</v>
+        <v>1064</v>
       </c>
       <c r="E119">
         <v>30</v>
@@ -4905,36 +4899,36 @@
         <v>12</v>
       </c>
       <c r="H119">
-        <v>102</v>
+        <v>532</v>
       </c>
       <c r="I119" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C120">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D120">
-        <v>1064</v>
+        <v>1809</v>
       </c>
       <c r="E120">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F120" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G120" t="s">
         <v>12</v>
       </c>
       <c r="H120">
-        <v>532</v>
+        <v>904</v>
       </c>
       <c r="I120" t="s">
         <v>16</v>
@@ -4942,16 +4936,16 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B121" t="s">
         <v>267</v>
       </c>
       <c r="C121">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D121">
-        <v>1809</v>
+        <v>2333</v>
       </c>
       <c r="E121">
         <v>60</v>
@@ -4963,24 +4957,24 @@
         <v>12</v>
       </c>
       <c r="H121">
-        <v>904</v>
+        <v>1555</v>
       </c>
       <c r="I121" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B122" t="s">
         <v>269</v>
       </c>
       <c r="C122">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D122">
-        <v>2333</v>
+        <v>1761</v>
       </c>
       <c r="E122">
         <v>60</v>
@@ -4992,24 +4986,24 @@
         <v>12</v>
       </c>
       <c r="H122">
-        <v>1555</v>
+        <v>1057</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B123" t="s">
         <v>271</v>
       </c>
       <c r="C123">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D123">
-        <v>1761</v>
+        <v>1103</v>
       </c>
       <c r="E123">
         <v>60</v>
@@ -5021,15 +5015,15 @@
         <v>12</v>
       </c>
       <c r="H123">
-        <v>1057</v>
+        <v>552</v>
       </c>
       <c r="I123" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B124" t="s">
         <v>273</v>
@@ -5038,7 +5032,7 @@
         <v>120</v>
       </c>
       <c r="D124">
-        <v>1103</v>
+        <v>1457</v>
       </c>
       <c r="E124">
         <v>60</v>
@@ -5050,7 +5044,7 @@
         <v>12</v>
       </c>
       <c r="H124">
-        <v>552</v>
+        <v>728</v>
       </c>
       <c r="I124" t="s">
         <v>13</v>
@@ -5058,16 +5052,16 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B125" t="s">
         <v>275</v>
       </c>
       <c r="C125">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D125">
-        <v>1457</v>
+        <v>2130</v>
       </c>
       <c r="E125">
         <v>60</v>
@@ -5079,24 +5073,24 @@
         <v>12</v>
       </c>
       <c r="H125">
-        <v>728</v>
+        <v>2556</v>
       </c>
       <c r="I125" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B126" t="s">
         <v>277</v>
       </c>
       <c r="C126">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D126">
-        <v>2130</v>
+        <v>1792</v>
       </c>
       <c r="E126">
         <v>60</v>
@@ -5108,7 +5102,7 @@
         <v>12</v>
       </c>
       <c r="H126">
-        <v>2556</v>
+        <v>1792</v>
       </c>
       <c r="I126" t="s">
         <v>19</v>
@@ -5116,45 +5110,45 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B127" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127">
+        <v>120</v>
+      </c>
+      <c r="D127">
+        <v>2234</v>
+      </c>
+      <c r="E127">
+        <v>60</v>
+      </c>
+      <c r="F127" t="s">
         <v>279</v>
       </c>
-      <c r="C127">
-        <v>60</v>
-      </c>
-      <c r="D127">
-        <v>1792</v>
-      </c>
-      <c r="E127">
-        <v>60</v>
-      </c>
-      <c r="F127" t="s">
-        <v>280</v>
-      </c>
       <c r="G127" t="s">
         <v>12</v>
       </c>
       <c r="H127">
-        <v>1792</v>
+        <v>1117</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B128" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C128">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D128">
-        <v>2234</v>
+        <v>825</v>
       </c>
       <c r="E128">
         <v>60</v>
@@ -5166,24 +5160,24 @@
         <v>12</v>
       </c>
       <c r="H128">
-        <v>1117</v>
+        <v>825</v>
       </c>
       <c r="I128" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B129" t="s">
         <v>282</v>
       </c>
       <c r="C129">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D129">
-        <v>825</v>
+        <v>750</v>
       </c>
       <c r="E129">
         <v>60</v>
@@ -5195,7 +5189,7 @@
         <v>12</v>
       </c>
       <c r="H129">
-        <v>825</v>
+        <v>375</v>
       </c>
       <c r="I129" t="s">
         <v>13</v>
@@ -5203,28 +5197,28 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B130" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C130">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D130">
-        <v>750</v>
+        <v>235</v>
       </c>
       <c r="E130">
         <v>60</v>
       </c>
       <c r="F130" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G130" t="s">
         <v>12</v>
       </c>
       <c r="H130">
-        <v>375</v>
+        <v>470</v>
       </c>
       <c r="I130" t="s">
         <v>13</v>
@@ -5232,7 +5226,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B131" t="s">
         <v>287</v>
@@ -5241,7 +5235,7 @@
         <v>30</v>
       </c>
       <c r="D131">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="E131">
         <v>60</v>
@@ -5253,24 +5247,24 @@
         <v>12</v>
       </c>
       <c r="H131">
-        <v>470</v>
+        <v>526</v>
       </c>
       <c r="I131" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B132" t="s">
         <v>289</v>
       </c>
       <c r="C132">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D132">
-        <v>263</v>
+        <v>594</v>
       </c>
       <c r="E132">
         <v>60</v>
@@ -5282,24 +5276,24 @@
         <v>12</v>
       </c>
       <c r="H132">
-        <v>526</v>
+        <v>356</v>
       </c>
       <c r="I132" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B133" t="s">
         <v>291</v>
       </c>
       <c r="C133">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D133">
-        <v>594</v>
+        <v>1024</v>
       </c>
       <c r="E133">
         <v>60</v>
@@ -5311,15 +5305,15 @@
         <v>12</v>
       </c>
       <c r="H133">
-        <v>356</v>
+        <v>683</v>
       </c>
       <c r="I133" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B134" t="s">
         <v>293</v>
@@ -5328,7 +5322,7 @@
         <v>90</v>
       </c>
       <c r="D134">
-        <v>1024</v>
+        <v>1650</v>
       </c>
       <c r="E134">
         <v>60</v>
@@ -5340,24 +5334,24 @@
         <v>12</v>
       </c>
       <c r="H134">
-        <v>683</v>
+        <v>1100</v>
       </c>
       <c r="I134" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B135" t="s">
         <v>295</v>
       </c>
       <c r="C135">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D135">
-        <v>1650</v>
+        <v>899</v>
       </c>
       <c r="E135">
         <v>60</v>
@@ -5369,7 +5363,7 @@
         <v>12</v>
       </c>
       <c r="H135">
-        <v>1100</v>
+        <v>899</v>
       </c>
       <c r="I135" t="s">
         <v>19</v>
@@ -5377,7 +5371,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B136" t="s">
         <v>297</v>
@@ -5386,7 +5380,7 @@
         <v>60</v>
       </c>
       <c r="D136">
-        <v>899</v>
+        <v>263</v>
       </c>
       <c r="E136">
         <v>60</v>
@@ -5398,36 +5392,36 @@
         <v>12</v>
       </c>
       <c r="H136">
-        <v>899</v>
+        <v>263</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B137" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C137">
         <v>60</v>
       </c>
       <c r="D137">
-        <v>263</v>
+        <v>712</v>
       </c>
       <c r="E137">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F137" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G137" t="s">
         <v>12</v>
       </c>
       <c r="H137">
-        <v>263</v>
+        <v>356</v>
       </c>
       <c r="I137" t="s">
         <v>13</v>
@@ -5435,16 +5429,16 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B138" t="s">
         <v>302</v>
       </c>
       <c r="C138">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D138">
-        <v>712</v>
+        <v>595</v>
       </c>
       <c r="E138">
         <v>30</v>
@@ -5456,24 +5450,24 @@
         <v>12</v>
       </c>
       <c r="H138">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I138" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B139" t="s">
         <v>304</v>
       </c>
       <c r="C139">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D139">
-        <v>595</v>
+        <v>385</v>
       </c>
       <c r="E139">
         <v>30</v>
@@ -5485,24 +5479,24 @@
         <v>12</v>
       </c>
       <c r="H139">
-        <v>357</v>
+        <v>96</v>
       </c>
       <c r="I139" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B140" t="s">
         <v>306</v>
       </c>
       <c r="C140">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D140">
-        <v>385</v>
+        <v>481</v>
       </c>
       <c r="E140">
         <v>30</v>
@@ -5514,7 +5508,7 @@
         <v>12</v>
       </c>
       <c r="H140">
-        <v>96</v>
+        <v>241</v>
       </c>
       <c r="I140" t="s">
         <v>13</v>
@@ -5522,7 +5516,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B141" t="s">
         <v>308</v>
@@ -5531,7 +5525,7 @@
         <v>60</v>
       </c>
       <c r="D141">
-        <v>481</v>
+        <v>780</v>
       </c>
       <c r="E141">
         <v>30</v>
@@ -5543,15 +5537,15 @@
         <v>12</v>
       </c>
       <c r="H141">
-        <v>241</v>
+        <v>390</v>
       </c>
       <c r="I141" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B142" t="s">
         <v>310</v>
@@ -5560,7 +5554,7 @@
         <v>60</v>
       </c>
       <c r="D142">
-        <v>780</v>
+        <v>1656</v>
       </c>
       <c r="E142">
         <v>30</v>
@@ -5572,24 +5566,24 @@
         <v>12</v>
       </c>
       <c r="H142">
-        <v>390</v>
+        <v>828</v>
       </c>
       <c r="I142" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B143" t="s">
         <v>312</v>
       </c>
       <c r="C143">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D143">
-        <v>1656</v>
+        <v>901</v>
       </c>
       <c r="E143">
         <v>30</v>
@@ -5601,7 +5595,7 @@
         <v>12</v>
       </c>
       <c r="H143">
-        <v>828</v>
+        <v>901</v>
       </c>
       <c r="I143" t="s">
         <v>19</v>
@@ -5609,36 +5603,36 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B144" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C144">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D144">
-        <v>901</v>
+        <v>2566</v>
       </c>
       <c r="E144">
         <v>30</v>
       </c>
       <c r="F144" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G144" t="s">
         <v>12</v>
       </c>
       <c r="H144">
-        <v>901</v>
+        <v>1283</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B145" t="s">
         <v>317</v>
@@ -5647,7 +5641,7 @@
         <v>60</v>
       </c>
       <c r="D145">
-        <v>2566</v>
+        <v>8672</v>
       </c>
       <c r="E145">
         <v>30</v>
@@ -5659,24 +5653,24 @@
         <v>12</v>
       </c>
       <c r="H145">
-        <v>1283</v>
+        <v>4336</v>
       </c>
       <c r="I145" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B146" t="s">
         <v>319</v>
       </c>
       <c r="C146">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D146">
-        <v>8672</v>
+        <v>6418</v>
       </c>
       <c r="E146">
         <v>30</v>
@@ -5688,7 +5682,7 @@
         <v>12</v>
       </c>
       <c r="H146">
-        <v>4336</v>
+        <v>6418</v>
       </c>
       <c r="I146" t="s">
         <v>19</v>
@@ -5696,16 +5690,16 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B147" t="s">
         <v>321</v>
       </c>
       <c r="C147">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D147">
-        <v>6418</v>
+        <v>4309</v>
       </c>
       <c r="E147">
         <v>30</v>
@@ -5717,24 +5711,24 @@
         <v>12</v>
       </c>
       <c r="H147">
-        <v>6418</v>
+        <v>2154</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B148" t="s">
         <v>323</v>
       </c>
       <c r="C148">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D148">
-        <v>4309</v>
+        <v>605</v>
       </c>
       <c r="E148">
         <v>30</v>
@@ -5746,24 +5740,24 @@
         <v>12</v>
       </c>
       <c r="H148">
-        <v>2154</v>
+        <v>182</v>
       </c>
       <c r="I148" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B149" t="s">
         <v>325</v>
       </c>
       <c r="C149">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D149">
-        <v>605</v>
+        <v>2520</v>
       </c>
       <c r="E149">
         <v>30</v>
@@ -5775,7 +5769,7 @@
         <v>12</v>
       </c>
       <c r="H149">
-        <v>182</v>
+        <v>1260</v>
       </c>
       <c r="I149" t="s">
         <v>13</v>
@@ -5783,7 +5777,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B150" t="s">
         <v>327</v>
@@ -5792,7 +5786,7 @@
         <v>60</v>
       </c>
       <c r="D150">
-        <v>2520</v>
+        <v>5379</v>
       </c>
       <c r="E150">
         <v>30</v>
@@ -5804,15 +5798,15 @@
         <v>12</v>
       </c>
       <c r="H150">
-        <v>1260</v>
+        <v>2690</v>
       </c>
       <c r="I150" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B151" t="s">
         <v>329</v>
@@ -5821,7 +5815,7 @@
         <v>60</v>
       </c>
       <c r="D151">
-        <v>5379</v>
+        <v>2103</v>
       </c>
       <c r="E151">
         <v>30</v>
@@ -5833,36 +5827,36 @@
         <v>12</v>
       </c>
       <c r="H151">
-        <v>2690</v>
+        <v>1052</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="B152" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C152">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D152">
-        <v>2103</v>
+        <v>1026</v>
       </c>
       <c r="E152">
         <v>30</v>
       </c>
       <c r="F152" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G152" t="s">
         <v>12</v>
       </c>
       <c r="H152">
-        <v>1052</v>
+        <v>308</v>
       </c>
       <c r="I152" t="s">
         <v>13</v>
@@ -5870,16 +5864,16 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B153" t="s">
         <v>334</v>
       </c>
       <c r="C153">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D153">
-        <v>1026</v>
+        <v>961</v>
       </c>
       <c r="E153">
         <v>30</v>
@@ -5891,53 +5885,53 @@
         <v>12</v>
       </c>
       <c r="H153">
-        <v>308</v>
+        <v>480</v>
       </c>
       <c r="I153" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B154" t="s">
+        <v>332</v>
+      </c>
+      <c r="C154">
+        <v>100</v>
+      </c>
+      <c r="D154">
+        <v>1046</v>
+      </c>
+      <c r="E154">
+        <v>30</v>
+      </c>
+      <c r="F154" t="s">
         <v>336</v>
       </c>
-      <c r="C154">
-        <v>60</v>
-      </c>
-      <c r="D154">
-        <v>961</v>
-      </c>
-      <c r="E154">
-        <v>30</v>
-      </c>
-      <c r="F154" t="s">
-        <v>337</v>
-      </c>
       <c r="G154" t="s">
         <v>12</v>
       </c>
       <c r="H154">
-        <v>480</v>
+        <v>314</v>
       </c>
       <c r="I154" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B155" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C155">
         <v>100</v>
       </c>
       <c r="D155">
-        <v>1046</v>
+        <v>2455</v>
       </c>
       <c r="E155">
         <v>30</v>
@@ -5949,15 +5943,15 @@
         <v>12</v>
       </c>
       <c r="H155">
-        <v>314</v>
+        <v>736</v>
       </c>
       <c r="I155" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B156" t="s">
         <v>339</v>
@@ -5966,7 +5960,7 @@
         <v>100</v>
       </c>
       <c r="D156">
-        <v>2455</v>
+        <v>473</v>
       </c>
       <c r="E156">
         <v>30</v>
@@ -5978,24 +5972,24 @@
         <v>12</v>
       </c>
       <c r="H156">
-        <v>736</v>
+        <v>142</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B157" t="s">
         <v>341</v>
       </c>
       <c r="C157">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D157">
-        <v>473</v>
+        <v>727</v>
       </c>
       <c r="E157">
         <v>30</v>
@@ -6007,53 +6001,50 @@
         <v>12</v>
       </c>
       <c r="H157">
-        <v>142</v>
+        <v>364</v>
       </c>
       <c r="I157" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B158" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C158">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="D158">
-        <v>727</v>
+        <v>640</v>
       </c>
       <c r="E158">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F158" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G158" t="s">
         <v>12</v>
       </c>
       <c r="H158">
-        <v>364</v>
-      </c>
-      <c r="I158" t="s">
-        <v>16</v>
+        <v>480</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B159" t="s">
         <v>346</v>
       </c>
       <c r="C159">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D159">
-        <v>640</v>
+        <v>1411</v>
       </c>
       <c r="E159">
         <v>150</v>
@@ -6065,21 +6056,21 @@
         <v>12</v>
       </c>
       <c r="H159">
-        <v>480</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B160" t="s">
         <v>348</v>
       </c>
       <c r="C160">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D160">
-        <v>1411</v>
+        <v>660</v>
       </c>
       <c r="E160">
         <v>150</v>
@@ -6091,12 +6082,12 @@
         <v>12</v>
       </c>
       <c r="H160">
-        <v>423</v>
+        <v>495</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B161" t="s">
         <v>350</v>
@@ -6122,7 +6113,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B162" t="s">
         <v>352</v>
@@ -6131,7 +6122,7 @@
         <v>200</v>
       </c>
       <c r="D162">
-        <v>660</v>
+        <v>845</v>
       </c>
       <c r="E162">
         <v>150</v>
@@ -6143,12 +6134,12 @@
         <v>12</v>
       </c>
       <c r="H162">
-        <v>495</v>
+        <v>634</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B163" t="s">
         <v>354</v>
@@ -6157,7 +6148,7 @@
         <v>200</v>
       </c>
       <c r="D163">
-        <v>845</v>
+        <v>563</v>
       </c>
       <c r="E163">
         <v>150</v>
@@ -6169,21 +6160,21 @@
         <v>12</v>
       </c>
       <c r="H163">
-        <v>634</v>
+        <v>422</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B164" t="s">
         <v>356</v>
       </c>
       <c r="C164">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D164">
-        <v>563</v>
+        <v>1525</v>
       </c>
       <c r="E164">
         <v>150</v>
@@ -6195,12 +6186,12 @@
         <v>12</v>
       </c>
       <c r="H164">
-        <v>422</v>
+        <v>458</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B165" t="s">
         <v>358</v>
@@ -6209,7 +6200,7 @@
         <v>500</v>
       </c>
       <c r="D165">
-        <v>1525</v>
+        <v>1490</v>
       </c>
       <c r="E165">
         <v>150</v>
@@ -6221,21 +6212,21 @@
         <v>12</v>
       </c>
       <c r="H165">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B166" t="s">
         <v>360</v>
       </c>
       <c r="C166">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D166">
-        <v>1490</v>
+        <v>385</v>
       </c>
       <c r="E166">
         <v>150</v>
@@ -6247,21 +6238,21 @@
         <v>12</v>
       </c>
       <c r="H166">
-        <v>447</v>
+        <v>193</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B167" t="s">
         <v>362</v>
       </c>
       <c r="C167">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D167">
-        <v>385</v>
+        <v>668</v>
       </c>
       <c r="E167">
         <v>150</v>
@@ -6273,32 +6264,6 @@
         <v>12</v>
       </c>
       <c r="H167">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>345</v>
-      </c>
-      <c r="B168" t="s">
-        <v>364</v>
-      </c>
-      <c r="C168">
-        <v>200</v>
-      </c>
-      <c r="D168">
-        <v>668</v>
-      </c>
-      <c r="E168">
-        <v>150</v>
-      </c>
-      <c r="F168" t="s">
-        <v>365</v>
-      </c>
-      <c r="G168" t="s">
-        <v>12</v>
-      </c>
-      <c r="H168">
         <v>501</v>
       </c>
     </row>
